--- a/sealand/CheckListSealand.xlsx
+++ b/sealand/CheckListSealand.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karinabanda/Desktop/Proyectos/Reportes/Reportes Diarios/Sealend/proyecto/seland/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karinabanda/Desktop/Proyectos/Reportes/Reportes Diarios/Sealend/proyecto/sealand/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AE0D657-942C-764E-B6AA-BBD94825AE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52CCBD55-6ADD-5043-855D-B625E54BD192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
   <si>
     <t>CPU Utilization Last Hour</t>
   </si>
@@ -67,9 +67,6 @@
   </si>
   <si>
     <t>Disponibilidad de la URL / Página web</t>
-  </si>
-  <si>
-    <t>Free Storages Space Last Hour</t>
   </si>
   <si>
     <t>La revisión realizada se basa en los siguientes criterios:
@@ -200,7 +197,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -484,24 +481,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -516,10 +500,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -533,114 +513,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -649,6 +521,111 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -894,65 +871,57 @@
   <sheetData>
     <row r="1" spans="2:21" ht="15.75" customHeight="1"/>
     <row r="2" spans="2:21" ht="27" customHeight="1">
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="47"/>
-      <c r="L2" s="47"/>
-      <c r="M2" s="47"/>
-      <c r="O2" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="P2" s="41"/>
-      <c r="Q2" s="41"/>
-      <c r="R2" s="41"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="O2" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="P2" s="46"/>
+      <c r="Q2" s="46"/>
+      <c r="R2" s="46"/>
     </row>
     <row r="3" spans="2:21" ht="27" customHeight="1">
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="38"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="19" t="s">
+      <c r="D3" s="49"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="38"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="J3" s="38"/>
-      <c r="K3" s="42"/>
-      <c r="L3" s="43" t="s">
+      <c r="G3" s="49"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="M3" s="44"/>
-      <c r="O3" s="24" t="s">
+      <c r="J3" s="52"/>
+      <c r="O3" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="P3" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="24" t="s">
+      <c r="Q3" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="Q3" s="24" t="s">
+      <c r="R3" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="R3" s="24" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="4" spans="2:21" ht="22" customHeight="1">
-      <c r="B4" s="40"/>
+      <c r="B4" s="44"/>
       <c r="C4" s="2" t="s">
         <v>1</v>
       </c>
@@ -971,21 +940,12 @@
       <c r="H4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="K4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="L4" s="45"/>
-      <c r="M4" s="46"/>
-      <c r="O4" s="40"/>
-      <c r="P4" s="40"/>
-      <c r="Q4" s="40"/>
-      <c r="R4" s="40"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="54"/>
+      <c r="O4" s="44"/>
+      <c r="P4" s="44"/>
+      <c r="Q4" s="44"/>
+      <c r="R4" s="44"/>
     </row>
     <row r="5" spans="2:21" ht="15.75" customHeight="1">
       <c r="B5" s="1"/>
@@ -995,11 +955,8 @@
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="18"/>
-      <c r="M5" s="17"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="15"/>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
@@ -1016,26 +973,26 @@
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
-      <c r="S7" s="13"/>
-      <c r="T7" s="13"/>
-      <c r="U7" s="12"/>
+      <c r="S7" s="11"/>
+      <c r="T7" s="11"/>
+      <c r="U7" s="10"/>
     </row>
     <row r="8" spans="2:21" ht="22" customHeight="1">
-      <c r="B8" s="54" t="s">
+      <c r="B8" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="54"/>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
-      <c r="H8" s="51" t="s">
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="H8" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="I8" s="52"/>
-      <c r="J8" s="52"/>
-      <c r="K8" s="52"/>
-      <c r="L8" s="52"/>
-      <c r="M8" s="53"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="22"/>
+      <c r="K8" s="22"/>
+      <c r="L8" s="22"/>
+      <c r="M8" s="23"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
@@ -1047,16 +1004,16 @@
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
       <c r="F9" s="9"/>
-      <c r="H9" s="56"/>
-      <c r="I9" s="57"/>
-      <c r="J9" s="57"/>
-      <c r="K9" s="57"/>
-      <c r="L9" s="57"/>
-      <c r="M9" s="58"/>
-      <c r="O9" s="55"/>
-      <c r="P9" s="55"/>
-      <c r="Q9" s="55"/>
-      <c r="R9" s="55"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="20"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17"/>
+      <c r="R9" s="17"/>
     </row>
     <row r="10" spans="2:21" ht="15.75" customHeight="1">
       <c r="O10" s="5"/>
@@ -1071,12 +1028,12 @@
       <c r="R11" s="5"/>
     </row>
     <row r="12" spans="2:21" ht="23" customHeight="1">
-      <c r="B12" s="48" t="s">
+      <c r="B12" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="49"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="50"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="42"/>
       <c r="O12" s="5"/>
       <c r="P12" s="5"/>
       <c r="Q12" s="5"/>
@@ -1129,7 +1086,7 @@
       <c r="P16" s="5"/>
       <c r="Q16" s="5"/>
       <c r="R16" s="5"/>
-      <c r="U16" s="13"/>
+      <c r="U16" s="11"/>
     </row>
     <row r="17" spans="2:21" ht="15.75" customHeight="1">
       <c r="B17" s="6"/>
@@ -1140,7 +1097,7 @@
       <c r="P17" s="5"/>
       <c r="Q17" s="5"/>
       <c r="R17" s="5"/>
-      <c r="U17" s="13"/>
+      <c r="U17" s="11"/>
     </row>
     <row r="18" spans="2:21" ht="15.75" customHeight="1">
       <c r="B18" s="6"/>
@@ -1155,164 +1112,164 @@
       <c r="E19" s="5"/>
     </row>
     <row r="20" spans="2:21" ht="24" customHeight="1">
-      <c r="G20" s="34" t="s">
+      <c r="G20" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="H20" s="35"/>
-      <c r="I20" s="35"/>
-      <c r="J20" s="35"/>
-      <c r="K20" s="35"/>
-      <c r="L20" s="35"/>
-      <c r="M20" s="36"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="25"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="25"/>
+      <c r="L20" s="25"/>
+      <c r="M20" s="26"/>
     </row>
     <row r="21" spans="2:21" ht="15.75" customHeight="1">
-      <c r="G21" s="20"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="21"/>
-      <c r="K21" s="21"/>
-      <c r="L21" s="21"/>
-      <c r="M21" s="22"/>
+      <c r="G21" s="27"/>
+      <c r="H21" s="28"/>
+      <c r="I21" s="28"/>
+      <c r="J21" s="28"/>
+      <c r="K21" s="28"/>
+      <c r="L21" s="28"/>
+      <c r="M21" s="29"/>
     </row>
     <row r="22" spans="2:21" ht="15.75" customHeight="1">
-      <c r="G22" s="20"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="21"/>
-      <c r="K22" s="21"/>
-      <c r="L22" s="21"/>
-      <c r="M22" s="22"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="28"/>
+      <c r="I22" s="28"/>
+      <c r="J22" s="28"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="28"/>
+      <c r="M22" s="29"/>
     </row>
     <row r="23" spans="2:21" ht="15" customHeight="1">
-      <c r="G23" s="20"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="21"/>
-      <c r="K23" s="21"/>
-      <c r="L23" s="21"/>
-      <c r="M23" s="22"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="28"/>
+      <c r="M23" s="29"/>
     </row>
     <row r="25" spans="2:21" ht="17" customHeight="1"/>
     <row r="26" spans="2:21" ht="24" customHeight="1">
-      <c r="G26" s="14" t="s">
+      <c r="G26" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="15"/>
-      <c r="L26" s="15"/>
-      <c r="M26" s="16"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="13"/>
+      <c r="M26" s="14"/>
     </row>
     <row r="27" spans="2:21" ht="15.75" customHeight="1">
-      <c r="G27" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
-      <c r="J27" s="26"/>
-      <c r="K27" s="26"/>
-      <c r="L27" s="26"/>
-      <c r="M27" s="27"/>
+      <c r="G27" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="H27" s="32"/>
+      <c r="I27" s="32"/>
+      <c r="J27" s="32"/>
+      <c r="K27" s="32"/>
+      <c r="L27" s="32"/>
+      <c r="M27" s="33"/>
     </row>
     <row r="28" spans="2:21" ht="15.75" customHeight="1">
-      <c r="G28" s="28"/>
-      <c r="H28" s="37"/>
-      <c r="I28" s="37"/>
-      <c r="J28" s="37"/>
-      <c r="K28" s="37"/>
-      <c r="L28" s="37"/>
-      <c r="M28" s="29"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="35"/>
+      <c r="I28" s="35"/>
+      <c r="J28" s="35"/>
+      <c r="K28" s="35"/>
+      <c r="L28" s="35"/>
+      <c r="M28" s="36"/>
     </row>
     <row r="29" spans="2:21" ht="15" customHeight="1">
-      <c r="G29" s="28"/>
-      <c r="H29" s="37"/>
-      <c r="I29" s="37"/>
-      <c r="J29" s="37"/>
-      <c r="K29" s="37"/>
-      <c r="L29" s="37"/>
-      <c r="M29" s="29"/>
+      <c r="G29" s="34"/>
+      <c r="H29" s="35"/>
+      <c r="I29" s="35"/>
+      <c r="J29" s="35"/>
+      <c r="K29" s="35"/>
+      <c r="L29" s="35"/>
+      <c r="M29" s="36"/>
     </row>
     <row r="30" spans="2:21" ht="15.75" customHeight="1">
-      <c r="G30" s="28"/>
-      <c r="H30" s="37"/>
-      <c r="I30" s="37"/>
-      <c r="J30" s="37"/>
-      <c r="K30" s="37"/>
-      <c r="L30" s="37"/>
-      <c r="M30" s="29"/>
+      <c r="G30" s="34"/>
+      <c r="H30" s="35"/>
+      <c r="I30" s="35"/>
+      <c r="J30" s="35"/>
+      <c r="K30" s="35"/>
+      <c r="L30" s="35"/>
+      <c r="M30" s="36"/>
     </row>
     <row r="31" spans="2:21" ht="15.75" customHeight="1">
-      <c r="G31" s="28"/>
-      <c r="H31" s="37"/>
-      <c r="I31" s="37"/>
-      <c r="J31" s="37"/>
-      <c r="K31" s="37"/>
-      <c r="L31" s="37"/>
-      <c r="M31" s="29"/>
+      <c r="G31" s="34"/>
+      <c r="H31" s="35"/>
+      <c r="I31" s="35"/>
+      <c r="J31" s="35"/>
+      <c r="K31" s="35"/>
+      <c r="L31" s="35"/>
+      <c r="M31" s="36"/>
     </row>
     <row r="32" spans="2:21" ht="15.75" customHeight="1">
-      <c r="G32" s="28"/>
-      <c r="H32" s="37"/>
-      <c r="I32" s="37"/>
-      <c r="J32" s="37"/>
-      <c r="K32" s="37"/>
-      <c r="L32" s="37"/>
-      <c r="M32" s="29"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="35"/>
+      <c r="I32" s="35"/>
+      <c r="J32" s="35"/>
+      <c r="K32" s="35"/>
+      <c r="L32" s="35"/>
+      <c r="M32" s="36"/>
     </row>
     <row r="33" spans="7:13" ht="15.75" customHeight="1">
-      <c r="G33" s="28"/>
-      <c r="H33" s="37"/>
-      <c r="I33" s="37"/>
-      <c r="J33" s="37"/>
-      <c r="K33" s="37"/>
-      <c r="L33" s="37"/>
-      <c r="M33" s="29"/>
+      <c r="G33" s="34"/>
+      <c r="H33" s="35"/>
+      <c r="I33" s="35"/>
+      <c r="J33" s="35"/>
+      <c r="K33" s="35"/>
+      <c r="L33" s="35"/>
+      <c r="M33" s="36"/>
     </row>
     <row r="34" spans="7:13" ht="15.75" customHeight="1">
-      <c r="G34" s="28"/>
-      <c r="H34" s="37"/>
-      <c r="I34" s="37"/>
-      <c r="J34" s="37"/>
-      <c r="K34" s="37"/>
-      <c r="L34" s="37"/>
-      <c r="M34" s="29"/>
+      <c r="G34" s="34"/>
+      <c r="H34" s="35"/>
+      <c r="I34" s="35"/>
+      <c r="J34" s="35"/>
+      <c r="K34" s="35"/>
+      <c r="L34" s="35"/>
+      <c r="M34" s="36"/>
     </row>
     <row r="35" spans="7:13" ht="15.75" customHeight="1">
-      <c r="G35" s="28"/>
-      <c r="H35" s="37"/>
-      <c r="I35" s="37"/>
-      <c r="J35" s="37"/>
-      <c r="K35" s="37"/>
-      <c r="L35" s="37"/>
-      <c r="M35" s="29"/>
+      <c r="G35" s="34"/>
+      <c r="H35" s="35"/>
+      <c r="I35" s="35"/>
+      <c r="J35" s="35"/>
+      <c r="K35" s="35"/>
+      <c r="L35" s="35"/>
+      <c r="M35" s="36"/>
     </row>
     <row r="36" spans="7:13" ht="15.75" customHeight="1">
-      <c r="G36" s="28"/>
-      <c r="H36" s="37"/>
-      <c r="I36" s="37"/>
-      <c r="J36" s="37"/>
-      <c r="K36" s="37"/>
-      <c r="L36" s="37"/>
-      <c r="M36" s="29"/>
+      <c r="G36" s="34"/>
+      <c r="H36" s="35"/>
+      <c r="I36" s="35"/>
+      <c r="J36" s="35"/>
+      <c r="K36" s="35"/>
+      <c r="L36" s="35"/>
+      <c r="M36" s="36"/>
     </row>
     <row r="37" spans="7:13" ht="15.75" customHeight="1">
-      <c r="G37" s="28"/>
-      <c r="H37" s="37"/>
-      <c r="I37" s="37"/>
-      <c r="J37" s="37"/>
-      <c r="K37" s="37"/>
-      <c r="L37" s="37"/>
-      <c r="M37" s="29"/>
+      <c r="G37" s="34"/>
+      <c r="H37" s="35"/>
+      <c r="I37" s="35"/>
+      <c r="J37" s="35"/>
+      <c r="K37" s="35"/>
+      <c r="L37" s="35"/>
+      <c r="M37" s="36"/>
     </row>
     <row r="38" spans="7:13" ht="15.75" customHeight="1">
-      <c r="G38" s="30"/>
-      <c r="H38" s="31"/>
-      <c r="I38" s="31"/>
-      <c r="J38" s="31"/>
-      <c r="K38" s="31"/>
-      <c r="L38" s="31"/>
-      <c r="M38" s="32"/>
+      <c r="G38" s="37"/>
+      <c r="H38" s="38"/>
+      <c r="I38" s="38"/>
+      <c r="J38" s="38"/>
+      <c r="K38" s="38"/>
+      <c r="L38" s="38"/>
+      <c r="M38" s="39"/>
     </row>
     <row r="39" spans="7:13" ht="15.75" customHeight="1"/>
     <row r="40" spans="7:13" ht="15.75" customHeight="1"/>
@@ -2278,26 +2235,25 @@
     <row r="1000" ht="15.75" customHeight="1"/>
     <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="18">
+    <mergeCell ref="G27:M38"/>
+    <mergeCell ref="G23:M23"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="R3:R4"/>
+    <mergeCell ref="O2:R2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="I3:J4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="B2:J2"/>
     <mergeCell ref="H8:M8"/>
     <mergeCell ref="G20:M20"/>
     <mergeCell ref="G21:M21"/>
     <mergeCell ref="G22:M22"/>
     <mergeCell ref="B8:F8"/>
-    <mergeCell ref="G27:M38"/>
-    <mergeCell ref="G23:M23"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="R3:R4"/>
-    <mergeCell ref="O2:R2"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="L3:M4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="Q3:Q4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>

--- a/sealand/CheckListSealand.xlsx
+++ b/sealand/CheckListSealand.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karinabanda/Desktop/Proyectos/Reportes/Reportes Diarios/Sealend/proyecto/sealand/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52CCBD55-6ADD-5043-855D-B625E54BD192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87227A49-83BC-AD4B-9522-30D21EC42F36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,16 +51,7 @@
     <t>Date Last Snapshot</t>
   </si>
   <si>
-    <t>RDS CLOUDWATCH</t>
-  </si>
-  <si>
-    <t>Metrics</t>
-  </si>
-  <si>
     <t>Notas</t>
-  </si>
-  <si>
-    <t>ERROR EN LOS LOGS EN "darrow-database-web"</t>
   </si>
   <si>
     <t>Id de la Instancia</t>
@@ -91,12 +82,21 @@
   <si>
     <t>Lambdas</t>
   </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>LOGS EN "darrow-database-web"</t>
+  </si>
+  <si>
+    <t>Free Storage  Last Hour</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="8">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -123,24 +123,6 @@
       <name val="Aptos Narrow"/>
     </font>
     <font>
-      <sz val="20"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="14"/>
       <color theme="0"/>
       <name val="Aptos Narrow (Cuerpo)"/>
@@ -152,8 +134,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="15"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow (Cuerpo)"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -180,12 +167,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFA9C"/>
-        <bgColor rgb="FF93C47D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="1" tint="0.249977111117893"/>
         <bgColor rgb="FF8ED873"/>
       </patternFill>
@@ -196,6 +177,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FF8ED873"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="25">
     <border>
@@ -469,48 +462,32 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -523,36 +500,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -565,9 +512,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -580,15 +524,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -601,32 +536,92 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -852,435 +847,479 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:U1001"/>
+  <dimension ref="B1:V1001"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3.6640625" customWidth="1"/>
     <col min="2" max="2" width="39.5" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.5" customWidth="1"/>
     <col min="4" max="4" width="12.5" customWidth="1"/>
     <col min="5" max="5" width="15.6640625" customWidth="1"/>
     <col min="6" max="6" width="10.5" customWidth="1"/>
     <col min="7" max="7" width="13.33203125" customWidth="1"/>
     <col min="8" max="13" width="10.5" customWidth="1"/>
-    <col min="14" max="14" width="10.33203125" customWidth="1"/>
-    <col min="15" max="15" width="49.6640625" customWidth="1"/>
-    <col min="16" max="18" width="15.6640625" customWidth="1"/>
-    <col min="19" max="26" width="10.5" customWidth="1"/>
+    <col min="14" max="15" width="10.33203125" customWidth="1"/>
+    <col min="16" max="16" width="49.6640625" customWidth="1"/>
+    <col min="17" max="19" width="15.6640625" customWidth="1"/>
+    <col min="20" max="27" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="15.75" customHeight="1"/>
-    <row r="2" spans="2:21" ht="27" customHeight="1">
-      <c r="B2" s="47" t="s">
+    <row r="1" spans="2:22" ht="15.75" customHeight="1"/>
+    <row r="2" spans="2:22" ht="27" customHeight="1">
+      <c r="B2" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="O2" s="45" t="s">
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="42"/>
+      <c r="M2" s="42"/>
+      <c r="N2" s="42"/>
+      <c r="P2" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="26"/>
+    </row>
+    <row r="3" spans="2:22" ht="27" customHeight="1">
+      <c r="B3" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="56" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="28"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="28"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="P2" s="46"/>
-      <c r="Q2" s="46"/>
-      <c r="R2" s="46"/>
-    </row>
-    <row r="3" spans="2:21" ht="27" customHeight="1">
-      <c r="B3" s="43" t="s">
+      <c r="K3" s="28"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="N3" s="31"/>
+      <c r="O3" s="54"/>
+      <c r="P3" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="49"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="48" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="49"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="51" t="s">
-        <v>7</v>
-      </c>
-      <c r="J3" s="52"/>
-      <c r="O3" s="43" t="s">
+      <c r="Q3" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="R3" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="S3" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="P3" s="43" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q3" s="43" t="s">
-        <v>17</v>
-      </c>
-      <c r="R3" s="43" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="2:21" ht="22" customHeight="1">
-      <c r="B4" s="44"/>
-      <c r="C4" s="2" t="s">
+    </row>
+    <row r="4" spans="2:22" ht="22" customHeight="1">
+      <c r="B4" s="57"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="53"/>
-      <c r="J4" s="54"/>
-      <c r="O4" s="44"/>
-      <c r="P4" s="44"/>
-      <c r="Q4" s="44"/>
-      <c r="R4" s="44"/>
-    </row>
-    <row r="5" spans="2:21" ht="15.75" customHeight="1">
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
+      <c r="J4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4" s="32"/>
+      <c r="N4" s="33"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="24"/>
+      <c r="Q4" s="24"/>
+      <c r="R4" s="24"/>
+      <c r="S4" s="24"/>
+    </row>
+    <row r="5" spans="2:22" ht="15.75" customHeight="1">
+      <c r="B5" s="39"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="41"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="15"/>
-      <c r="O5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="53"/>
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
-    </row>
-    <row r="6" spans="2:21" ht="15.75" customHeight="1">
-      <c r="O6" s="1"/>
+      <c r="S5" s="1"/>
+    </row>
+    <row r="6" spans="2:22" ht="15.75" customHeight="1">
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
-    </row>
-    <row r="7" spans="2:21" ht="16" customHeight="1">
-      <c r="O7" s="1"/>
+      <c r="S6" s="1"/>
+    </row>
+    <row r="7" spans="2:22" ht="16" customHeight="1">
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
-      <c r="S7" s="11"/>
-      <c r="T7" s="11"/>
-      <c r="U7" s="10"/>
-    </row>
-    <row r="8" spans="2:21" ht="22" customHeight="1">
-      <c r="B8" s="30" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="H8" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" s="22"/>
-      <c r="J8" s="22"/>
-      <c r="K8" s="22"/>
-      <c r="L8" s="22"/>
-      <c r="M8" s="23"/>
-      <c r="O8" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="8"/>
+      <c r="U7" s="8"/>
+      <c r="V7" s="7"/>
+    </row>
+    <row r="8" spans="2:22" ht="22" customHeight="1">
+      <c r="B8" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="H8" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" s="36"/>
+      <c r="J8" s="36"/>
+      <c r="K8" s="36"/>
+      <c r="L8" s="36"/>
+      <c r="M8" s="37"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
-    </row>
-    <row r="9" spans="2:21" ht="15.75" customHeight="1">
-      <c r="B9" s="7"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="9"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="20"/>
-      <c r="O9" s="17"/>
-      <c r="P9" s="17"/>
-      <c r="Q9" s="17"/>
-      <c r="R9" s="17"/>
-    </row>
-    <row r="10" spans="2:21" ht="15.75" customHeight="1">
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
-      <c r="R10" s="5"/>
-    </row>
-    <row r="11" spans="2:21" ht="24" customHeight="1">
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
-      <c r="R11" s="5"/>
-    </row>
-    <row r="12" spans="2:21" ht="23" customHeight="1">
-      <c r="B12" s="40" t="s">
+      <c r="S8" s="1"/>
+    </row>
+    <row r="9" spans="2:22" ht="15.75" customHeight="1">
+      <c r="B9" s="4"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="6"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="14"/>
+      <c r="P9" s="11"/>
+      <c r="Q9" s="11"/>
+      <c r="R9" s="11"/>
+      <c r="S9" s="11"/>
+    </row>
+    <row r="10" spans="2:22" ht="15.75" customHeight="1">
+      <c r="B10" s="4"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="6"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="2:22" ht="14" customHeight="1">
+      <c r="B11" s="4"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="6"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="2:22" ht="13" customHeight="1">
+      <c r="B12" s="4"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="6"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="2:22" ht="15.75" customHeight="1">
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3"/>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="2:22" ht="15.75" customHeight="1">
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="3"/>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="2:22" ht="15.75" customHeight="1">
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="3"/>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="2:22" ht="23" customHeight="1">
+      <c r="B16" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="47"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+      <c r="V16" s="8"/>
+    </row>
+    <row r="17" spans="2:22" ht="15.75" customHeight="1">
+      <c r="B17" s="43"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="44"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="45"/>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3"/>
+      <c r="S17" s="3"/>
+      <c r="V17" s="8"/>
+    </row>
+    <row r="18" spans="2:22" ht="15.75" customHeight="1">
+      <c r="B18" s="43"/>
+      <c r="C18" s="44"/>
+      <c r="D18" s="44"/>
+      <c r="E18" s="44"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="45"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3"/>
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="2:22" ht="17" customHeight="1">
+      <c r="B19" s="52"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="52"/>
+      <c r="F19" s="52"/>
+      <c r="G19" s="52"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="2:22" ht="14" customHeight="1">
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3"/>
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="2:22" ht="15.75" customHeight="1">
+      <c r="P21" s="3"/>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3"/>
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="2:22" ht="24" customHeight="1">
+      <c r="B22" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="42"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="5"/>
-      <c r="R12" s="5"/>
-    </row>
-    <row r="13" spans="2:21" ht="15.75" customHeight="1">
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="5"/>
-      <c r="R13" s="5"/>
-    </row>
-    <row r="14" spans="2:21" ht="15.75" customHeight="1">
-      <c r="B14" s="6"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="5"/>
-      <c r="R14" s="5"/>
-    </row>
-    <row r="15" spans="2:21" ht="15.75" customHeight="1">
-      <c r="B15" s="6"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="5"/>
-      <c r="R15" s="5"/>
-    </row>
-    <row r="16" spans="2:21" ht="15.75" customHeight="1">
-      <c r="B16" s="6"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="5"/>
-      <c r="R16" s="5"/>
-      <c r="U16" s="11"/>
-    </row>
-    <row r="17" spans="2:21" ht="15.75" customHeight="1">
-      <c r="B17" s="6"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="O17" s="5"/>
-      <c r="P17" s="5"/>
-      <c r="Q17" s="5"/>
-      <c r="R17" s="5"/>
-      <c r="U17" s="11"/>
-    </row>
-    <row r="18" spans="2:21" ht="15.75" customHeight="1">
-      <c r="B18" s="6"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-    </row>
-    <row r="19" spans="2:21" ht="17" customHeight="1">
-      <c r="B19" s="6"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-    </row>
-    <row r="20" spans="2:21" ht="24" customHeight="1">
-      <c r="G20" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="H20" s="25"/>
-      <c r="I20" s="25"/>
-      <c r="J20" s="25"/>
-      <c r="K20" s="25"/>
-      <c r="L20" s="25"/>
-      <c r="M20" s="26"/>
-    </row>
-    <row r="21" spans="2:21" ht="15.75" customHeight="1">
-      <c r="G21" s="27"/>
-      <c r="H21" s="28"/>
-      <c r="I21" s="28"/>
-      <c r="J21" s="28"/>
-      <c r="K21" s="28"/>
-      <c r="L21" s="28"/>
-      <c r="M21" s="29"/>
-    </row>
-    <row r="22" spans="2:21" ht="15.75" customHeight="1">
-      <c r="G22" s="27"/>
-      <c r="H22" s="28"/>
-      <c r="I22" s="28"/>
-      <c r="J22" s="28"/>
-      <c r="K22" s="28"/>
-      <c r="L22" s="28"/>
-      <c r="M22" s="29"/>
-    </row>
-    <row r="23" spans="2:21" ht="15" customHeight="1">
-      <c r="G23" s="27"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="28"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="28"/>
-      <c r="M23" s="29"/>
-    </row>
-    <row r="25" spans="2:21" ht="17" customHeight="1"/>
-    <row r="26" spans="2:21" ht="24" customHeight="1">
-      <c r="G26" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
-      <c r="L26" s="13"/>
-      <c r="M26" s="14"/>
-    </row>
-    <row r="27" spans="2:21" ht="15.75" customHeight="1">
-      <c r="G27" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="H27" s="32"/>
-      <c r="I27" s="32"/>
-      <c r="J27" s="32"/>
-      <c r="K27" s="32"/>
-      <c r="L27" s="32"/>
-      <c r="M27" s="33"/>
-    </row>
-    <row r="28" spans="2:21" ht="15.75" customHeight="1">
-      <c r="G28" s="34"/>
-      <c r="H28" s="35"/>
-      <c r="I28" s="35"/>
-      <c r="J28" s="35"/>
-      <c r="K28" s="35"/>
-      <c r="L28" s="35"/>
-      <c r="M28" s="36"/>
-    </row>
-    <row r="29" spans="2:21" ht="15" customHeight="1">
-      <c r="G29" s="34"/>
-      <c r="H29" s="35"/>
-      <c r="I29" s="35"/>
-      <c r="J29" s="35"/>
-      <c r="K29" s="35"/>
-      <c r="L29" s="35"/>
-      <c r="M29" s="36"/>
-    </row>
-    <row r="30" spans="2:21" ht="15.75" customHeight="1">
-      <c r="G30" s="34"/>
-      <c r="H30" s="35"/>
-      <c r="I30" s="35"/>
-      <c r="J30" s="35"/>
-      <c r="K30" s="35"/>
-      <c r="L30" s="35"/>
-      <c r="M30" s="36"/>
-    </row>
-    <row r="31" spans="2:21" ht="15.75" customHeight="1">
-      <c r="G31" s="34"/>
-      <c r="H31" s="35"/>
-      <c r="I31" s="35"/>
-      <c r="J31" s="35"/>
-      <c r="K31" s="35"/>
-      <c r="L31" s="35"/>
-      <c r="M31" s="36"/>
-    </row>
-    <row r="32" spans="2:21" ht="15.75" customHeight="1">
-      <c r="G32" s="34"/>
-      <c r="H32" s="35"/>
-      <c r="I32" s="35"/>
-      <c r="J32" s="35"/>
-      <c r="K32" s="35"/>
-      <c r="L32" s="35"/>
-      <c r="M32" s="36"/>
-    </row>
-    <row r="33" spans="7:13" ht="15.75" customHeight="1">
-      <c r="G33" s="34"/>
-      <c r="H33" s="35"/>
-      <c r="I33" s="35"/>
-      <c r="J33" s="35"/>
-      <c r="K33" s="35"/>
-      <c r="L33" s="35"/>
-      <c r="M33" s="36"/>
-    </row>
-    <row r="34" spans="7:13" ht="15.75" customHeight="1">
-      <c r="G34" s="34"/>
-      <c r="H34" s="35"/>
-      <c r="I34" s="35"/>
-      <c r="J34" s="35"/>
-      <c r="K34" s="35"/>
-      <c r="L34" s="35"/>
-      <c r="M34" s="36"/>
-    </row>
-    <row r="35" spans="7:13" ht="15.75" customHeight="1">
-      <c r="G35" s="34"/>
-      <c r="H35" s="35"/>
-      <c r="I35" s="35"/>
-      <c r="J35" s="35"/>
-      <c r="K35" s="35"/>
-      <c r="L35" s="35"/>
-      <c r="M35" s="36"/>
-    </row>
-    <row r="36" spans="7:13" ht="15.75" customHeight="1">
-      <c r="G36" s="34"/>
-      <c r="H36" s="35"/>
-      <c r="I36" s="35"/>
-      <c r="J36" s="35"/>
-      <c r="K36" s="35"/>
-      <c r="L36" s="35"/>
-      <c r="M36" s="36"/>
-    </row>
-    <row r="37" spans="7:13" ht="15.75" customHeight="1">
-      <c r="G37" s="34"/>
-      <c r="H37" s="35"/>
-      <c r="I37" s="35"/>
-      <c r="J37" s="35"/>
-      <c r="K37" s="35"/>
-      <c r="L37" s="35"/>
-      <c r="M37" s="36"/>
-    </row>
-    <row r="38" spans="7:13" ht="15.75" customHeight="1">
-      <c r="G38" s="37"/>
-      <c r="H38" s="38"/>
-      <c r="I38" s="38"/>
-      <c r="J38" s="38"/>
-      <c r="K38" s="38"/>
-      <c r="L38" s="38"/>
-      <c r="M38" s="39"/>
-    </row>
-    <row r="39" spans="7:13" ht="15.75" customHeight="1"/>
-    <row r="40" spans="7:13" ht="15.75" customHeight="1"/>
-    <row r="41" spans="7:13" ht="15.75" customHeight="1"/>
-    <row r="42" spans="7:13" ht="15.75" customHeight="1"/>
-    <row r="43" spans="7:13" ht="15.75" customHeight="1"/>
-    <row r="44" spans="7:13" ht="15.75" customHeight="1"/>
-    <row r="45" spans="7:13" ht="15.75" customHeight="1"/>
-    <row r="46" spans="7:13" ht="15.75" customHeight="1"/>
-    <row r="47" spans="7:13" ht="15.75" customHeight="1"/>
-    <row r="48" spans="7:13" ht="15.75" customHeight="1"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="49"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="49"/>
+      <c r="G22" s="50"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="2:22" ht="15" customHeight="1">
+      <c r="B23" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="17"/>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3"/>
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="2:22" ht="15" customHeight="1">
+      <c r="B24" s="18"/>
+      <c r="C24" s="51"/>
+      <c r="D24" s="51"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="51"/>
+      <c r="G24" s="19"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="2:22" ht="17" customHeight="1">
+      <c r="B25" s="18"/>
+      <c r="C25" s="51"/>
+      <c r="D25" s="51"/>
+      <c r="E25" s="51"/>
+      <c r="F25" s="51"/>
+      <c r="G25" s="19"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3"/>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="2:22" ht="15" customHeight="1">
+      <c r="B26" s="18"/>
+      <c r="C26" s="51"/>
+      <c r="D26" s="51"/>
+      <c r="E26" s="51"/>
+      <c r="F26" s="51"/>
+      <c r="G26" s="19"/>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="3"/>
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="2:22" ht="15.75" customHeight="1">
+      <c r="B27" s="18"/>
+      <c r="C27" s="51"/>
+      <c r="D27" s="51"/>
+      <c r="E27" s="51"/>
+      <c r="F27" s="51"/>
+      <c r="G27" s="19"/>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="3"/>
+      <c r="R27" s="3"/>
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="2:22" ht="15.75" customHeight="1">
+      <c r="B28" s="18"/>
+      <c r="C28" s="51"/>
+      <c r="D28" s="51"/>
+      <c r="E28" s="51"/>
+      <c r="F28" s="51"/>
+      <c r="G28" s="19"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="3"/>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="2:22" ht="15" customHeight="1">
+      <c r="B29" s="18"/>
+      <c r="C29" s="51"/>
+      <c r="D29" s="51"/>
+      <c r="E29" s="51"/>
+      <c r="F29" s="51"/>
+      <c r="G29" s="19"/>
+      <c r="P29" s="3"/>
+      <c r="Q29" s="3"/>
+      <c r="R29" s="3"/>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="2:22" ht="15.75" customHeight="1">
+      <c r="B30" s="18"/>
+      <c r="C30" s="51"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="51"/>
+      <c r="G30" s="19"/>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="3"/>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="2:22" ht="15.75" customHeight="1">
+      <c r="B31" s="18"/>
+      <c r="C31" s="51"/>
+      <c r="D31" s="51"/>
+      <c r="E31" s="51"/>
+      <c r="F31" s="51"/>
+      <c r="G31" s="19"/>
+      <c r="P31" s="3"/>
+      <c r="Q31" s="3"/>
+      <c r="R31" s="3"/>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="2:22" ht="15.75" customHeight="1">
+      <c r="B32" s="18"/>
+      <c r="C32" s="51"/>
+      <c r="D32" s="51"/>
+      <c r="E32" s="51"/>
+      <c r="F32" s="51"/>
+      <c r="G32" s="19"/>
+      <c r="P32" s="3"/>
+      <c r="Q32" s="3"/>
+      <c r="R32" s="3"/>
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:7" ht="15.75" customHeight="1">
+      <c r="B33" s="18"/>
+      <c r="C33" s="51"/>
+      <c r="D33" s="51"/>
+      <c r="E33" s="51"/>
+      <c r="F33" s="51"/>
+      <c r="G33" s="19"/>
+    </row>
+    <row r="34" spans="2:7" ht="15.75" customHeight="1">
+      <c r="B34" s="20"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="22"/>
+    </row>
+    <row r="35" spans="2:7" ht="15.75" customHeight="1"/>
+    <row r="36" spans="2:7" ht="15.75" customHeight="1"/>
+    <row r="37" spans="2:7" ht="15.75" customHeight="1"/>
+    <row r="38" spans="2:7" ht="15.75" customHeight="1"/>
+    <row r="39" spans="2:7" ht="15.75" customHeight="1"/>
+    <row r="40" spans="2:7" ht="15.75" customHeight="1"/>
+    <row r="41" spans="2:7" ht="15.75" customHeight="1"/>
+    <row r="42" spans="2:7" ht="15.75" customHeight="1"/>
+    <row r="43" spans="2:7" ht="15.75" customHeight="1"/>
+    <row r="44" spans="2:7" ht="15.75" customHeight="1"/>
+    <row r="45" spans="2:7" ht="15.75" customHeight="1"/>
+    <row r="46" spans="2:7" ht="15.75" customHeight="1"/>
+    <row r="47" spans="2:7" ht="15.75" customHeight="1"/>
+    <row r="48" spans="2:7" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
@@ -2235,25 +2274,27 @@
     <row r="1000" ht="15.75" customHeight="1"/>
     <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="G27:M38"/>
-    <mergeCell ref="G23:M23"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="R3:R4"/>
-    <mergeCell ref="O2:R2"/>
+  <mergeCells count="20">
+    <mergeCell ref="B23:G34"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="S3:S4"/>
+    <mergeCell ref="P2:S2"/>
     <mergeCell ref="B3:B4"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="I3:J4"/>
-    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="M3:N4"/>
     <mergeCell ref="P3:P4"/>
     <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="B2:J2"/>
+    <mergeCell ref="R3:R4"/>
     <mergeCell ref="H8:M8"/>
-    <mergeCell ref="G20:M20"/>
-    <mergeCell ref="G21:M21"/>
-    <mergeCell ref="G22:M22"/>
-    <mergeCell ref="B8:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>

--- a/sealand/CheckListSealand.xlsx
+++ b/sealand/CheckListSealand.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karinabanda/Desktop/Proyectos/Reportes/Reportes Diarios/Sealend/proyecto/sealand/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87227A49-83BC-AD4B-9522-30D21EC42F36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3BF6FE1-AE65-9744-B305-E118EE672DD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
   <si>
     <t>CPU Utilization Last Hour</t>
   </si>
@@ -60,14 +60,6 @@
     <t>Disponibilidad de la URL / Página web</t>
   </si>
   <si>
-    <t>La revisión realizada se basa en los siguientes criterios:
-* Status Check: Verificación del estado de la instancia, asegurando que el sistema y el volumen se encuentren en "OK".
-* CPU Utilization: Confirmación de que el uso de CPU se mantenga por debajo del 85%, tanto en las instancias como en la RDS.
-* Snapshot: Validación de la creación del respaldo correspondiente al día anterior en la RDS.
-* Free Storage Space: Verificación de que el espacio libre en la RDS sea superior a 10 GB.
-Recomendación: No depender únicamente de los comentarios anexados; se sugiere realizar una revisión adicional para mayor precisión.</t>
-  </si>
-  <si>
     <t>Nombre de la función</t>
   </si>
   <si>
@@ -89,14 +81,17 @@
     <t>LOGS EN "darrow-database-web"</t>
   </si>
   <si>
-    <t>Free Storage  Last Hour</t>
+    <t>La revisión realizada se basa en los siguientes criterios:
+* CPU Utilization: Confirmación de que el uso de CPU se mantenga por debajo del 85%.
+* Snapshot: Validación de la creación del respaldo correspondiente al día anterior en la RDS.
+Recomendación: No depender únicamente de los comentarios anexados; se sugiere realizar una revisión adicional para mayor precisión.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -139,8 +134,13 @@
       <color theme="1"/>
       <name val="Aptos Narrow (Cuerpo)"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -183,12 +183,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FF8ED873"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="25">
     <border>
@@ -476,7 +470,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -500,128 +494,133 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -847,7 +846,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:V1001"/>
+  <dimension ref="B1:U1001"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3.6640625" customWidth="1"/>
@@ -858,80 +857,71 @@
     <col min="6" max="6" width="10.5" customWidth="1"/>
     <col min="7" max="7" width="13.33203125" customWidth="1"/>
     <col min="8" max="13" width="10.5" customWidth="1"/>
-    <col min="14" max="15" width="10.33203125" customWidth="1"/>
-    <col min="16" max="16" width="49.6640625" customWidth="1"/>
-    <col min="17" max="19" width="15.6640625" customWidth="1"/>
-    <col min="20" max="27" width="10.5" customWidth="1"/>
+    <col min="14" max="14" width="10.33203125" customWidth="1"/>
+    <col min="15" max="15" width="49.6640625" customWidth="1"/>
+    <col min="16" max="18" width="15.6640625" customWidth="1"/>
+    <col min="19" max="26" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" ht="15.75" customHeight="1"/>
-    <row r="2" spans="2:22" ht="27" customHeight="1">
-      <c r="B2" s="34" t="s">
+    <row r="1" spans="2:21" ht="15.75" customHeight="1"/>
+    <row r="2" spans="2:21" ht="27" customHeight="1">
+      <c r="B2" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="42"/>
-      <c r="N2" s="42"/>
-      <c r="P2" s="25" t="s">
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
+      <c r="O2" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="P2" s="36"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+    </row>
+    <row r="3" spans="2:21" ht="27" customHeight="1">
+      <c r="B3" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="26"/>
-      <c r="R2" s="26"/>
-      <c r="S2" s="26"/>
-    </row>
-    <row r="3" spans="2:22" ht="27" customHeight="1">
-      <c r="B3" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="56" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="28" t="s">
+      <c r="D3" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="28"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="27" t="s">
+      <c r="E3" s="30"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="28"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" s="28"/>
-      <c r="L3" s="29"/>
-      <c r="M3" s="30" t="s">
+      <c r="H3" s="30"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="N3" s="31"/>
-      <c r="O3" s="54"/>
-      <c r="P3" s="23" t="s">
+      <c r="K3" s="40"/>
+      <c r="O3" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="P3" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="23" t="s">
+      <c r="Q3" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="R3" s="23" t="s">
+      <c r="R3" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="S3" s="23" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="2:22" ht="22" customHeight="1">
-      <c r="B4" s="57"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="40" t="s">
+    </row>
+    <row r="4" spans="2:21" ht="22" customHeight="1">
+      <c r="B4" s="38"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="16" t="s">
         <v>1</v>
       </c>
       <c r="E4" s="2" t="s">
@@ -949,362 +939,349 @@
       <c r="I4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4" s="32"/>
-      <c r="N4" s="33"/>
-      <c r="O4" s="54"/>
-      <c r="P4" s="24"/>
-      <c r="Q4" s="24"/>
-      <c r="R4" s="24"/>
-      <c r="S4" s="24"/>
-    </row>
-    <row r="5" spans="2:22" ht="15.75" customHeight="1">
-      <c r="B5" s="39"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="42"/>
+      <c r="O4" s="34"/>
+      <c r="P4" s="34"/>
+      <c r="Q4" s="34"/>
+      <c r="R4" s="34"/>
+    </row>
+    <row r="5" spans="2:21" ht="15.75" customHeight="1">
+      <c r="B5" s="15"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="41"/>
+      <c r="D5" s="17"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="53"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="9"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="1"/>
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
-      <c r="S5" s="1"/>
-    </row>
-    <row r="6" spans="2:22" ht="15.75" customHeight="1">
+    </row>
+    <row r="6" spans="2:21" ht="15.75" customHeight="1">
+      <c r="O6" s="1"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
-      <c r="S6" s="1"/>
-    </row>
-    <row r="7" spans="2:22" ht="16" customHeight="1">
+    </row>
+    <row r="7" spans="2:21" ht="16" customHeight="1">
+      <c r="O7" s="1"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
-      <c r="S7" s="1"/>
+      <c r="S7" s="8"/>
       <c r="T7" s="8"/>
-      <c r="U7" s="8"/>
-      <c r="V7" s="7"/>
-    </row>
-    <row r="8" spans="2:22" ht="22" customHeight="1">
-      <c r="B8" s="38" t="s">
-        <v>18</v>
+      <c r="U7" s="7"/>
+    </row>
+    <row r="8" spans="2:21" ht="22" customHeight="1">
+      <c r="B8" s="19" t="s">
+        <v>17</v>
       </c>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="H8" s="35" t="s">
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="H8" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="I8" s="36"/>
-      <c r="J8" s="36"/>
-      <c r="K8" s="36"/>
-      <c r="L8" s="36"/>
-      <c r="M8" s="37"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="44"/>
+      <c r="K8" s="44"/>
+      <c r="L8" s="44"/>
+      <c r="M8" s="45"/>
+      <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
-    </row>
-    <row r="9" spans="2:22" ht="15.75" customHeight="1">
-      <c r="B9" s="4"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="6"/>
+    </row>
+    <row r="9" spans="2:21" ht="15.75" customHeight="1">
+      <c r="B9" s="56"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="58"/>
       <c r="H9" s="12"/>
       <c r="I9" s="13"/>
       <c r="J9" s="13"/>
       <c r="K9" s="13"/>
       <c r="L9" s="13"/>
       <c r="M9" s="14"/>
+      <c r="O9" s="11"/>
       <c r="P9" s="11"/>
       <c r="Q9" s="11"/>
       <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-    </row>
-    <row r="10" spans="2:22" ht="15.75" customHeight="1">
+    </row>
+    <row r="10" spans="2:21" ht="15.75" customHeight="1">
       <c r="B10" s="4"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
       <c r="F10" s="6"/>
+      <c r="O10" s="3"/>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
-    </row>
-    <row r="11" spans="2:22" ht="14" customHeight="1">
+    </row>
+    <row r="11" spans="2:21" ht="14" customHeight="1">
       <c r="B11" s="4"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
       <c r="F11" s="6"/>
+      <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="2:22" ht="13" customHeight="1">
+    </row>
+    <row r="12" spans="2:21" ht="13" customHeight="1">
       <c r="B12" s="4"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
       <c r="F12" s="6"/>
+      <c r="O12" s="3"/>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
-      <c r="S12" s="3"/>
-    </row>
-    <row r="13" spans="2:22" ht="15.75" customHeight="1">
+    </row>
+    <row r="13" spans="2:21" ht="15.75" customHeight="1">
+      <c r="O13" s="3"/>
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
-    </row>
-    <row r="14" spans="2:22" ht="15.75" customHeight="1">
+    </row>
+    <row r="14" spans="2:21" ht="15.75" customHeight="1">
+      <c r="O14" s="3"/>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
-      <c r="S14" s="3"/>
-    </row>
-    <row r="15" spans="2:22" ht="15.75" customHeight="1">
+    </row>
+    <row r="15" spans="2:21" ht="15.75" customHeight="1">
+      <c r="O15" s="3"/>
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
-      <c r="S15" s="3"/>
-    </row>
-    <row r="16" spans="2:22" ht="23" customHeight="1">
-      <c r="B16" s="46" t="s">
+    </row>
+    <row r="16" spans="2:21" ht="23" customHeight="1">
+      <c r="B16" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="47"/>
-      <c r="D16" s="47"/>
-      <c r="E16" s="47"/>
-      <c r="F16" s="47"/>
-      <c r="G16" s="47"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-      <c r="S16" s="3"/>
-      <c r="V16" s="8"/>
-    </row>
-    <row r="17" spans="2:22" ht="15.75" customHeight="1">
-      <c r="B17" s="43"/>
-      <c r="C17" s="44"/>
-      <c r="D17" s="44"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="45"/>
+      <c r="U16" s="8"/>
+    </row>
+    <row r="17" spans="2:21" ht="15.75" customHeight="1">
+      <c r="B17" s="24"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="26"/>
+      <c r="O17" s="3"/>
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
-      <c r="S17" s="3"/>
-      <c r="V17" s="8"/>
-    </row>
-    <row r="18" spans="2:22" ht="15.75" customHeight="1">
-      <c r="B18" s="43"/>
-      <c r="C18" s="44"/>
-      <c r="D18" s="44"/>
-      <c r="E18" s="44"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="45"/>
+      <c r="U17" s="8"/>
+    </row>
+    <row r="18" spans="2:21" ht="15.75" customHeight="1">
+      <c r="B18" s="24"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="26"/>
+      <c r="O18" s="3"/>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
-      <c r="S18" s="3"/>
-    </row>
-    <row r="19" spans="2:22" ht="17" customHeight="1">
-      <c r="B19" s="52"/>
-      <c r="C19" s="52"/>
-      <c r="D19" s="52"/>
-      <c r="E19" s="52"/>
-      <c r="F19" s="52"/>
-      <c r="G19" s="52"/>
+    </row>
+    <row r="19" spans="2:21" ht="17" customHeight="1">
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-      <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="2:22" ht="14" customHeight="1">
+    </row>
+    <row r="20" spans="2:21" ht="14" customHeight="1">
+      <c r="O20" s="3"/>
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
       <c r="R20" s="3"/>
-      <c r="S20" s="3"/>
-    </row>
-    <row r="21" spans="2:22" ht="15.75" customHeight="1">
+    </row>
+    <row r="21" spans="2:21" ht="15.75" customHeight="1">
+      <c r="O21" s="3"/>
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
-      <c r="S21" s="3"/>
-    </row>
-    <row r="22" spans="2:22" ht="24" customHeight="1">
-      <c r="B22" s="48" t="s">
+    </row>
+    <row r="22" spans="2:21" ht="24" customHeight="1">
+      <c r="B22" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="49"/>
-      <c r="D22" s="49"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="49"/>
-      <c r="G22" s="50"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="23"/>
+      <c r="O22" s="3"/>
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
-      <c r="S22" s="3"/>
-    </row>
-    <row r="23" spans="2:22" ht="15" customHeight="1">
-      <c r="B23" s="15" t="s">
-        <v>11</v>
+    </row>
+    <row r="23" spans="2:21" ht="15" customHeight="1">
+      <c r="B23" s="47" t="s">
+        <v>18</v>
       </c>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="17"/>
+      <c r="C23" s="48"/>
+      <c r="D23" s="48"/>
+      <c r="E23" s="48"/>
+      <c r="F23" s="48"/>
+      <c r="G23" s="49"/>
+      <c r="O23" s="3"/>
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
-      <c r="S23" s="3"/>
-    </row>
-    <row r="24" spans="2:22" ht="15" customHeight="1">
-      <c r="B24" s="18"/>
+    </row>
+    <row r="24" spans="2:21" ht="15" customHeight="1">
+      <c r="B24" s="50"/>
       <c r="C24" s="51"/>
       <c r="D24" s="51"/>
       <c r="E24" s="51"/>
       <c r="F24" s="51"/>
-      <c r="G24" s="19"/>
+      <c r="G24" s="52"/>
+      <c r="O24" s="3"/>
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
       <c r="R24" s="3"/>
-      <c r="S24" s="3"/>
-    </row>
-    <row r="25" spans="2:22" ht="17" customHeight="1">
-      <c r="B25" s="18"/>
+    </row>
+    <row r="25" spans="2:21" ht="17" customHeight="1">
+      <c r="B25" s="50"/>
       <c r="C25" s="51"/>
       <c r="D25" s="51"/>
       <c r="E25" s="51"/>
       <c r="F25" s="51"/>
-      <c r="G25" s="19"/>
+      <c r="G25" s="52"/>
+      <c r="O25" s="3"/>
       <c r="P25" s="3"/>
       <c r="Q25" s="3"/>
       <c r="R25" s="3"/>
-      <c r="S25" s="3"/>
-    </row>
-    <row r="26" spans="2:22" ht="15" customHeight="1">
-      <c r="B26" s="18"/>
+    </row>
+    <row r="26" spans="2:21" ht="15" customHeight="1">
+      <c r="B26" s="50"/>
       <c r="C26" s="51"/>
       <c r="D26" s="51"/>
       <c r="E26" s="51"/>
       <c r="F26" s="51"/>
-      <c r="G26" s="19"/>
+      <c r="G26" s="52"/>
+      <c r="O26" s="3"/>
       <c r="P26" s="3"/>
       <c r="Q26" s="3"/>
       <c r="R26" s="3"/>
-      <c r="S26" s="3"/>
-    </row>
-    <row r="27" spans="2:22" ht="15.75" customHeight="1">
-      <c r="B27" s="18"/>
+    </row>
+    <row r="27" spans="2:21" ht="15.75" customHeight="1">
+      <c r="B27" s="50"/>
       <c r="C27" s="51"/>
       <c r="D27" s="51"/>
       <c r="E27" s="51"/>
       <c r="F27" s="51"/>
-      <c r="G27" s="19"/>
+      <c r="G27" s="52"/>
+      <c r="O27" s="3"/>
       <c r="P27" s="3"/>
       <c r="Q27" s="3"/>
       <c r="R27" s="3"/>
-      <c r="S27" s="3"/>
-    </row>
-    <row r="28" spans="2:22" ht="15.75" customHeight="1">
-      <c r="B28" s="18"/>
+    </row>
+    <row r="28" spans="2:21" ht="15.75" customHeight="1">
+      <c r="B28" s="50"/>
       <c r="C28" s="51"/>
       <c r="D28" s="51"/>
       <c r="E28" s="51"/>
       <c r="F28" s="51"/>
-      <c r="G28" s="19"/>
+      <c r="G28" s="52"/>
+      <c r="O28" s="3"/>
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
       <c r="R28" s="3"/>
-      <c r="S28" s="3"/>
-    </row>
-    <row r="29" spans="2:22" ht="15" customHeight="1">
-      <c r="B29" s="18"/>
+    </row>
+    <row r="29" spans="2:21" ht="15" customHeight="1">
+      <c r="B29" s="50"/>
       <c r="C29" s="51"/>
       <c r="D29" s="51"/>
       <c r="E29" s="51"/>
       <c r="F29" s="51"/>
-      <c r="G29" s="19"/>
+      <c r="G29" s="52"/>
+      <c r="O29" s="3"/>
       <c r="P29" s="3"/>
       <c r="Q29" s="3"/>
       <c r="R29" s="3"/>
-      <c r="S29" s="3"/>
-    </row>
-    <row r="30" spans="2:22" ht="15.75" customHeight="1">
-      <c r="B30" s="18"/>
+    </row>
+    <row r="30" spans="2:21" ht="15.75" customHeight="1">
+      <c r="B30" s="50"/>
       <c r="C30" s="51"/>
       <c r="D30" s="51"/>
       <c r="E30" s="51"/>
       <c r="F30" s="51"/>
-      <c r="G30" s="19"/>
+      <c r="G30" s="52"/>
+      <c r="O30" s="3"/>
       <c r="P30" s="3"/>
       <c r="Q30" s="3"/>
       <c r="R30" s="3"/>
-      <c r="S30" s="3"/>
-    </row>
-    <row r="31" spans="2:22" ht="15.75" customHeight="1">
-      <c r="B31" s="18"/>
+    </row>
+    <row r="31" spans="2:21" ht="15.75" customHeight="1">
+      <c r="B31" s="50"/>
       <c r="C31" s="51"/>
       <c r="D31" s="51"/>
       <c r="E31" s="51"/>
       <c r="F31" s="51"/>
-      <c r="G31" s="19"/>
+      <c r="G31" s="52"/>
+      <c r="O31" s="3"/>
       <c r="P31" s="3"/>
       <c r="Q31" s="3"/>
       <c r="R31" s="3"/>
-      <c r="S31" s="3"/>
-    </row>
-    <row r="32" spans="2:22" ht="15.75" customHeight="1">
-      <c r="B32" s="18"/>
+    </row>
+    <row r="32" spans="2:21" ht="15.75" customHeight="1">
+      <c r="B32" s="50"/>
       <c r="C32" s="51"/>
       <c r="D32" s="51"/>
       <c r="E32" s="51"/>
       <c r="F32" s="51"/>
-      <c r="G32" s="19"/>
+      <c r="G32" s="52"/>
+      <c r="O32" s="3"/>
       <c r="P32" s="3"/>
       <c r="Q32" s="3"/>
       <c r="R32" s="3"/>
-      <c r="S32" s="3"/>
     </row>
     <row r="33" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B33" s="18"/>
+      <c r="B33" s="50"/>
       <c r="C33" s="51"/>
       <c r="D33" s="51"/>
       <c r="E33" s="51"/>
       <c r="F33" s="51"/>
-      <c r="G33" s="19"/>
+      <c r="G33" s="52"/>
     </row>
     <row r="34" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B34" s="20"/>
-      <c r="C34" s="21"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="21"/>
-      <c r="G34" s="22"/>
+      <c r="B34" s="53"/>
+      <c r="C34" s="54"/>
+      <c r="D34" s="54"/>
+      <c r="E34" s="54"/>
+      <c r="F34" s="54"/>
+      <c r="G34" s="55"/>
     </row>
     <row r="35" spans="2:7" ht="15.75" customHeight="1"/>
     <row r="36" spans="2:7" ht="15.75" customHeight="1"/>
@@ -2275,6 +2252,18 @@
     <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="R3:R4"/>
+    <mergeCell ref="O2:R2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="J3:K4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="B23:G34"/>
     <mergeCell ref="B19:G19"/>
     <mergeCell ref="B8:F8"/>
@@ -2283,18 +2272,6 @@
     <mergeCell ref="B18:G18"/>
     <mergeCell ref="B17:G17"/>
     <mergeCell ref="B16:G16"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="B2:N2"/>
-    <mergeCell ref="S3:S4"/>
-    <mergeCell ref="P2:S2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="M3:N4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="R3:R4"/>
-    <mergeCell ref="H8:M8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>

--- a/sealand/CheckListSealand.xlsx
+++ b/sealand/CheckListSealand.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karinabanda/Desktop/Proyectos/Reportes/Reportes Diarios/Sealend/proyecto/sealand/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3BF6FE1-AE65-9744-B305-E118EE672DD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF78F3CD-BFFF-C94D-A085-6340FD71CAE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -470,35 +470,113 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -531,96 +609,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -865,63 +853,63 @@
   <sheetData>
     <row r="1" spans="2:21" ht="15.75" customHeight="1"/>
     <row r="2" spans="2:21" ht="27" customHeight="1">
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="O2" s="35" t="s">
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="O2" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="36"/>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
     </row>
     <row r="3" spans="2:21" ht="27" customHeight="1">
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="30"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="29" t="s">
+      <c r="E3" s="27"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="30"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="39" t="s">
+      <c r="H3" s="27"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="40"/>
-      <c r="O3" s="33" t="s">
+      <c r="K3" s="30"/>
+      <c r="O3" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="P3" s="33" t="s">
+      <c r="P3" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="33" t="s">
+      <c r="Q3" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="R3" s="33" t="s">
+      <c r="R3" s="20" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="2:21" ht="22" customHeight="1">
-      <c r="B4" s="38"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="16" t="s">
+      <c r="B4" s="25"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="10" t="s">
         <v>1</v>
       </c>
       <c r="E4" s="2" t="s">
@@ -939,25 +927,25 @@
       <c r="I4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="41"/>
-      <c r="K4" s="42"/>
-      <c r="O4" s="34"/>
-      <c r="P4" s="34"/>
-      <c r="Q4" s="34"/>
-      <c r="R4" s="34"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="32"/>
+      <c r="O4" s="21"/>
+      <c r="P4" s="21"/>
+      <c r="Q4" s="21"/>
+      <c r="R4" s="21"/>
     </row>
     <row r="5" spans="2:21" ht="15.75" customHeight="1">
-      <c r="B5" s="15"/>
+      <c r="B5" s="9"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="17"/>
+      <c r="D5" s="11"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="9"/>
-      <c r="N5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="6"/>
+      <c r="N5" s="4"/>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
@@ -974,76 +962,76 @@
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
-      <c r="S7" s="8"/>
-      <c r="T7" s="8"/>
-      <c r="U7" s="7"/>
+      <c r="S7" s="5"/>
+      <c r="T7" s="5"/>
+      <c r="U7" s="4"/>
     </row>
     <row r="8" spans="2:21" ht="22" customHeight="1">
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="H8" s="43" t="s">
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="H8" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="I8" s="44"/>
-      <c r="J8" s="44"/>
-      <c r="K8" s="44"/>
-      <c r="L8" s="44"/>
-      <c r="M8" s="45"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="14"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
     </row>
     <row r="9" spans="2:21" ht="15.75" customHeight="1">
-      <c r="B9" s="56"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="58"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="14"/>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="19"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="19"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="8"/>
     </row>
     <row r="10" spans="2:21" ht="15.75" customHeight="1">
-      <c r="B10" s="4"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="6"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="19"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
     </row>
     <row r="11" spans="2:21" ht="14" customHeight="1">
-      <c r="B11" s="4"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="6"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="19"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
     </row>
     <row r="12" spans="2:21" ht="13" customHeight="1">
-      <c r="B12" s="4"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="6"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="19"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
@@ -1068,52 +1056,52 @@
       <c r="R15" s="3"/>
     </row>
     <row r="16" spans="2:21" ht="23" customHeight="1">
-      <c r="B16" s="27" t="s">
+      <c r="B16" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="28"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
+      <c r="F16" s="52"/>
+      <c r="G16" s="52"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-      <c r="U16" s="8"/>
+      <c r="U16" s="5"/>
     </row>
     <row r="17" spans="2:21" ht="15.75" customHeight="1">
-      <c r="B17" s="24"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="26"/>
+      <c r="B17" s="48"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="49"/>
+      <c r="E17" s="49"/>
+      <c r="F17" s="49"/>
+      <c r="G17" s="50"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
-      <c r="U17" s="8"/>
+      <c r="U17" s="5"/>
     </row>
     <row r="18" spans="2:21" ht="15.75" customHeight="1">
-      <c r="B18" s="24"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="26"/>
+      <c r="B18" s="48"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="49"/>
+      <c r="G18" s="50"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
     </row>
     <row r="19" spans="2:21" ht="17" customHeight="1">
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="42"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
@@ -1132,156 +1120,156 @@
       <c r="R21" s="3"/>
     </row>
     <row r="22" spans="2:21" ht="24" customHeight="1">
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="23"/>
+      <c r="C22" s="46"/>
+      <c r="D22" s="46"/>
+      <c r="E22" s="46"/>
+      <c r="F22" s="46"/>
+      <c r="G22" s="47"/>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
     </row>
     <row r="23" spans="2:21" ht="15" customHeight="1">
-      <c r="B23" s="47" t="s">
+      <c r="B23" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="C23" s="48"/>
-      <c r="D23" s="48"/>
-      <c r="E23" s="48"/>
-      <c r="F23" s="48"/>
-      <c r="G23" s="49"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="35"/>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
     </row>
     <row r="24" spans="2:21" ht="15" customHeight="1">
-      <c r="B24" s="50"/>
-      <c r="C24" s="51"/>
-      <c r="D24" s="51"/>
-      <c r="E24" s="51"/>
-      <c r="F24" s="51"/>
-      <c r="G24" s="52"/>
+      <c r="B24" s="36"/>
+      <c r="C24" s="37"/>
+      <c r="D24" s="37"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="38"/>
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
       <c r="R24" s="3"/>
     </row>
     <row r="25" spans="2:21" ht="17" customHeight="1">
-      <c r="B25" s="50"/>
-      <c r="C25" s="51"/>
-      <c r="D25" s="51"/>
-      <c r="E25" s="51"/>
-      <c r="F25" s="51"/>
-      <c r="G25" s="52"/>
+      <c r="B25" s="36"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="38"/>
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
       <c r="Q25" s="3"/>
       <c r="R25" s="3"/>
     </row>
     <row r="26" spans="2:21" ht="15" customHeight="1">
-      <c r="B26" s="50"/>
-      <c r="C26" s="51"/>
-      <c r="D26" s="51"/>
-      <c r="E26" s="51"/>
-      <c r="F26" s="51"/>
-      <c r="G26" s="52"/>
+      <c r="B26" s="36"/>
+      <c r="C26" s="37"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="37"/>
+      <c r="G26" s="38"/>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
       <c r="Q26" s="3"/>
       <c r="R26" s="3"/>
     </row>
     <row r="27" spans="2:21" ht="15.75" customHeight="1">
-      <c r="B27" s="50"/>
-      <c r="C27" s="51"/>
-      <c r="D27" s="51"/>
-      <c r="E27" s="51"/>
-      <c r="F27" s="51"/>
-      <c r="G27" s="52"/>
+      <c r="B27" s="36"/>
+      <c r="C27" s="37"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="37"/>
+      <c r="G27" s="38"/>
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
       <c r="Q27" s="3"/>
       <c r="R27" s="3"/>
     </row>
     <row r="28" spans="2:21" ht="15.75" customHeight="1">
-      <c r="B28" s="50"/>
-      <c r="C28" s="51"/>
-      <c r="D28" s="51"/>
-      <c r="E28" s="51"/>
-      <c r="F28" s="51"/>
-      <c r="G28" s="52"/>
+      <c r="B28" s="36"/>
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="38"/>
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
       <c r="R28" s="3"/>
     </row>
     <row r="29" spans="2:21" ht="15" customHeight="1">
-      <c r="B29" s="50"/>
-      <c r="C29" s="51"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51"/>
-      <c r="F29" s="51"/>
-      <c r="G29" s="52"/>
+      <c r="B29" s="36"/>
+      <c r="C29" s="37"/>
+      <c r="D29" s="37"/>
+      <c r="E29" s="37"/>
+      <c r="F29" s="37"/>
+      <c r="G29" s="38"/>
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
       <c r="Q29" s="3"/>
       <c r="R29" s="3"/>
     </row>
     <row r="30" spans="2:21" ht="15.75" customHeight="1">
-      <c r="B30" s="50"/>
-      <c r="C30" s="51"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="51"/>
-      <c r="F30" s="51"/>
-      <c r="G30" s="52"/>
+      <c r="B30" s="36"/>
+      <c r="C30" s="37"/>
+      <c r="D30" s="37"/>
+      <c r="E30" s="37"/>
+      <c r="F30" s="37"/>
+      <c r="G30" s="38"/>
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
       <c r="Q30" s="3"/>
       <c r="R30" s="3"/>
     </row>
     <row r="31" spans="2:21" ht="15.75" customHeight="1">
-      <c r="B31" s="50"/>
-      <c r="C31" s="51"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="51"/>
-      <c r="F31" s="51"/>
-      <c r="G31" s="52"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="37"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="37"/>
+      <c r="F31" s="37"/>
+      <c r="G31" s="38"/>
       <c r="O31" s="3"/>
       <c r="P31" s="3"/>
       <c r="Q31" s="3"/>
       <c r="R31" s="3"/>
     </row>
     <row r="32" spans="2:21" ht="15.75" customHeight="1">
-      <c r="B32" s="50"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="51"/>
-      <c r="F32" s="51"/>
-      <c r="G32" s="52"/>
+      <c r="B32" s="36"/>
+      <c r="C32" s="37"/>
+      <c r="D32" s="37"/>
+      <c r="E32" s="37"/>
+      <c r="F32" s="37"/>
+      <c r="G32" s="38"/>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
       <c r="Q32" s="3"/>
       <c r="R32" s="3"/>
     </row>
     <row r="33" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B33" s="50"/>
-      <c r="C33" s="51"/>
-      <c r="D33" s="51"/>
-      <c r="E33" s="51"/>
-      <c r="F33" s="51"/>
-      <c r="G33" s="52"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="37"/>
+      <c r="D33" s="37"/>
+      <c r="E33" s="37"/>
+      <c r="F33" s="37"/>
+      <c r="G33" s="38"/>
     </row>
     <row r="34" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B34" s="53"/>
-      <c r="C34" s="54"/>
-      <c r="D34" s="54"/>
-      <c r="E34" s="54"/>
-      <c r="F34" s="54"/>
-      <c r="G34" s="55"/>
+      <c r="B34" s="39"/>
+      <c r="C34" s="40"/>
+      <c r="D34" s="40"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="41"/>
     </row>
     <row r="35" spans="2:7" ht="15.75" customHeight="1"/>
     <row r="36" spans="2:7" ht="15.75" customHeight="1"/>
@@ -2251,7 +2239,18 @@
     <row r="1000" ht="15.75" customHeight="1"/>
     <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="24">
+    <mergeCell ref="B23:G34"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
     <mergeCell ref="H8:M8"/>
     <mergeCell ref="B2:K2"/>
     <mergeCell ref="B9:F9"/>
@@ -2264,14 +2263,7 @@
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="P3:P4"/>
     <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="B23:G34"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="B17:G17"/>
-    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="H9:M9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>

--- a/sealand/CheckListSealand.xlsx
+++ b/sealand/CheckListSealand.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karinabanda/Desktop/Proyectos/Reportes/Reportes Diarios/Sealend/proyecto/sealand/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF78F3CD-BFFF-C94D-A085-6340FD71CAE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13CCD5E9-C00A-274F-B9DC-0562FE64B4D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="19">
   <si>
     <t>CPU Utilization Last Hour</t>
   </si>
@@ -184,7 +184,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -352,15 +352,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -461,16 +452,90 @@
       </left>
       <right/>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -479,14 +544,81 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -496,21 +628,6 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -523,12 +640,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -538,78 +649,36 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -834,7 +903,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:U1001"/>
+  <dimension ref="B1:V1001"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3.6640625" customWidth="1"/>
@@ -844,72 +913,80 @@
     <col min="5" max="5" width="15.6640625" customWidth="1"/>
     <col min="6" max="6" width="10.5" customWidth="1"/>
     <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="13" width="10.5" customWidth="1"/>
-    <col min="14" max="14" width="10.33203125" customWidth="1"/>
-    <col min="15" max="15" width="49.6640625" customWidth="1"/>
-    <col min="16" max="18" width="15.6640625" customWidth="1"/>
-    <col min="19" max="26" width="10.5" customWidth="1"/>
+    <col min="8" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="15" width="10.33203125" customWidth="1"/>
+    <col min="16" max="16" width="49.6640625" customWidth="1"/>
+    <col min="17" max="19" width="15.6640625" customWidth="1"/>
+    <col min="20" max="27" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="15.75" customHeight="1"/>
-    <row r="2" spans="2:21" ht="27" customHeight="1">
-      <c r="B2" s="15" t="s">
+    <row r="1" spans="2:22" ht="15.75" customHeight="1"/>
+    <row r="2" spans="2:22" ht="27" customHeight="1">
+      <c r="B2" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="O2" s="22" t="s">
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="49"/>
+      <c r="P2" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="23"/>
-      <c r="R2" s="23"/>
-    </row>
-    <row r="3" spans="2:21" ht="27" customHeight="1">
-      <c r="B3" s="24" t="s">
+      <c r="Q2" s="39"/>
+      <c r="R2" s="39"/>
+      <c r="S2" s="39"/>
+    </row>
+    <row r="3" spans="2:22" ht="27" customHeight="1">
+      <c r="B3" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="44" t="s">
+      <c r="C3" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="27"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="26" t="s">
+      <c r="E3" s="41"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="27"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="29" t="s">
+      <c r="H3" s="41"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="40" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" s="41"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="30"/>
-      <c r="O3" s="20" t="s">
+      <c r="N3" s="43"/>
+      <c r="P3" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="P3" s="20" t="s">
+      <c r="Q3" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="20" t="s">
+      <c r="R3" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="R3" s="20" t="s">
+      <c r="S3" s="36" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="22" customHeight="1">
-      <c r="B4" s="25"/>
-      <c r="C4" s="44"/>
-      <c r="D4" s="10" t="s">
+    <row r="4" spans="2:22" ht="22" customHeight="1">
+      <c r="B4" s="51"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="9" t="s">
         <v>1</v>
       </c>
       <c r="E4" s="2" t="s">
@@ -927,349 +1004,360 @@
       <c r="I4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="31"/>
-      <c r="K4" s="32"/>
-      <c r="O4" s="21"/>
-      <c r="P4" s="21"/>
-      <c r="Q4" s="21"/>
-      <c r="R4" s="21"/>
-    </row>
-    <row r="5" spans="2:21" ht="15.75" customHeight="1">
-      <c r="B5" s="9"/>
+      <c r="J4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4" s="46"/>
+      <c r="N4" s="44"/>
+      <c r="P4" s="37"/>
+      <c r="Q4" s="37"/>
+      <c r="R4" s="37"/>
+      <c r="S4" s="37"/>
+    </row>
+    <row r="5" spans="2:22" ht="15.75" customHeight="1">
+      <c r="B5" s="52"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="6"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="1"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="54"/>
+      <c r="L5" s="54"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="6"/>
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
-    </row>
-    <row r="6" spans="2:21" ht="15.75" customHeight="1">
-      <c r="O6" s="1"/>
+      <c r="S5" s="1"/>
+    </row>
+    <row r="6" spans="2:22" ht="15.75" customHeight="1">
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
-    </row>
-    <row r="7" spans="2:21" ht="16" customHeight="1">
-      <c r="O7" s="1"/>
+      <c r="S6" s="1"/>
+    </row>
+    <row r="7" spans="2:22" ht="16" customHeight="1">
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
-      <c r="S7" s="5"/>
+      <c r="S7" s="1"/>
       <c r="T7" s="5"/>
-      <c r="U7" s="4"/>
-    </row>
-    <row r="8" spans="2:21" ht="22" customHeight="1">
-      <c r="B8" s="43" t="s">
+      <c r="U7" s="5"/>
+      <c r="V7" s="4"/>
+    </row>
+    <row r="8" spans="2:22" ht="22" customHeight="1">
+      <c r="B8" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
-      <c r="H8" s="12" t="s">
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="H8" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="14"/>
-      <c r="O8" s="1"/>
+      <c r="I8" s="34"/>
+      <c r="J8" s="34"/>
+      <c r="K8" s="34"/>
+      <c r="L8" s="34"/>
+      <c r="M8" s="35"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
-    </row>
-    <row r="9" spans="2:21" ht="15.75" customHeight="1">
-      <c r="B9" s="17"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="19"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="18"/>
-      <c r="L9" s="18"/>
-      <c r="M9" s="19"/>
-      <c r="O9" s="8"/>
+      <c r="S8" s="1"/>
+    </row>
+    <row r="9" spans="2:22" ht="15.75" customHeight="1">
+      <c r="B9" s="30"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="32"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="31"/>
+      <c r="M9" s="32"/>
       <c r="P9" s="8"/>
       <c r="Q9" s="8"/>
       <c r="R9" s="8"/>
-    </row>
-    <row r="10" spans="2:21" ht="15.75" customHeight="1">
-      <c r="B10" s="17"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="19"/>
-      <c r="O10" s="3"/>
+      <c r="S9" s="8"/>
+    </row>
+    <row r="10" spans="2:22" ht="15.75" customHeight="1">
+      <c r="B10" s="30"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="32"/>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="2:21" ht="14" customHeight="1">
-      <c r="B11" s="17"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="19"/>
-      <c r="O11" s="3"/>
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="2:22" ht="14" customHeight="1">
+      <c r="B11" s="30"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="32"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="2:21" ht="13" customHeight="1">
-      <c r="B12" s="17"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="19"/>
-      <c r="O12" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="2:22" ht="13" customHeight="1">
+      <c r="B12" s="30"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="32"/>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="2:21" ht="15.75" customHeight="1">
-      <c r="O13" s="3"/>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="2:22" ht="15.75" customHeight="1">
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="2:21" ht="15.75" customHeight="1">
-      <c r="O14" s="3"/>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="2:22" ht="15.75" customHeight="1">
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="2:21" ht="15.75" customHeight="1">
-      <c r="O15" s="3"/>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="2:22" ht="15.75" customHeight="1">
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="2:21" ht="23" customHeight="1">
-      <c r="B16" s="51" t="s">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="2:22" ht="23" customHeight="1">
+      <c r="B16" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="52"/>
-      <c r="D16" s="52"/>
-      <c r="E16" s="52"/>
-      <c r="F16" s="52"/>
-      <c r="G16" s="52"/>
-      <c r="O16" s="3"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-      <c r="U16" s="5"/>
-    </row>
-    <row r="17" spans="2:21" ht="15.75" customHeight="1">
-      <c r="B17" s="48"/>
-      <c r="C17" s="49"/>
-      <c r="D17" s="49"/>
-      <c r="E17" s="49"/>
-      <c r="F17" s="49"/>
-      <c r="G17" s="50"/>
-      <c r="O17" s="3"/>
+      <c r="S16" s="3"/>
+      <c r="V16" s="5"/>
+    </row>
+    <row r="17" spans="2:22" ht="15.75" customHeight="1">
+      <c r="B17" s="25"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="27"/>
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
-      <c r="U17" s="5"/>
-    </row>
-    <row r="18" spans="2:21" ht="15.75" customHeight="1">
-      <c r="B18" s="48"/>
-      <c r="C18" s="49"/>
-      <c r="D18" s="49"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="49"/>
-      <c r="G18" s="50"/>
-      <c r="O18" s="3"/>
+      <c r="S17" s="3"/>
+      <c r="V17" s="5"/>
+    </row>
+    <row r="18" spans="2:22" ht="15.75" customHeight="1">
+      <c r="B18" s="25"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="27"/>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="2:21" ht="17" customHeight="1">
-      <c r="B19" s="42"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="42"/>
-      <c r="O19" s="3"/>
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="2:22" ht="17" customHeight="1">
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="2:21" ht="14" customHeight="1">
-      <c r="O20" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="2:22" ht="14" customHeight="1">
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
       <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="2:21" ht="15.75" customHeight="1">
-      <c r="O21" s="3"/>
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="2:22" ht="15.75" customHeight="1">
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="2:21" ht="24" customHeight="1">
-      <c r="B22" s="45" t="s">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="2:22" ht="24" customHeight="1">
+      <c r="B22" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="46"/>
-      <c r="D22" s="46"/>
-      <c r="E22" s="46"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="47"/>
-      <c r="O22" s="3"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="24"/>
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="2:21" ht="15" customHeight="1">
-      <c r="B23" s="33" t="s">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="2:22" ht="15" customHeight="1">
+      <c r="B23" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C23" s="34"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="35"/>
-      <c r="O23" s="3"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="12"/>
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="2:21" ht="15" customHeight="1">
-      <c r="B24" s="36"/>
-      <c r="C24" s="37"/>
-      <c r="D24" s="37"/>
-      <c r="E24" s="37"/>
-      <c r="F24" s="37"/>
-      <c r="G24" s="38"/>
-      <c r="O24" s="3"/>
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="2:22" ht="15" customHeight="1">
+      <c r="B24" s="13"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="15"/>
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
       <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="2:21" ht="17" customHeight="1">
-      <c r="B25" s="36"/>
-      <c r="C25" s="37"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="37"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="38"/>
-      <c r="O25" s="3"/>
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="2:22" ht="17" customHeight="1">
+      <c r="B25" s="13"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="15"/>
       <c r="P25" s="3"/>
       <c r="Q25" s="3"/>
       <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="2:21" ht="15" customHeight="1">
-      <c r="B26" s="36"/>
-      <c r="C26" s="37"/>
-      <c r="D26" s="37"/>
-      <c r="E26" s="37"/>
-      <c r="F26" s="37"/>
-      <c r="G26" s="38"/>
-      <c r="O26" s="3"/>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="2:22" ht="15" customHeight="1">
+      <c r="B26" s="13"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="15"/>
       <c r="P26" s="3"/>
       <c r="Q26" s="3"/>
       <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="2:21" ht="15.75" customHeight="1">
-      <c r="B27" s="36"/>
-      <c r="C27" s="37"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="37"/>
-      <c r="G27" s="38"/>
-      <c r="O27" s="3"/>
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="2:22" ht="15.75" customHeight="1">
+      <c r="B27" s="13"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="15"/>
       <c r="P27" s="3"/>
       <c r="Q27" s="3"/>
       <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="2:21" ht="15.75" customHeight="1">
-      <c r="B28" s="36"/>
-      <c r="C28" s="37"/>
-      <c r="D28" s="37"/>
-      <c r="E28" s="37"/>
-      <c r="F28" s="37"/>
-      <c r="G28" s="38"/>
-      <c r="O28" s="3"/>
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="2:22" ht="15.75" customHeight="1">
+      <c r="B28" s="13"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="15"/>
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
       <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="2:21" ht="15" customHeight="1">
-      <c r="B29" s="36"/>
-      <c r="C29" s="37"/>
-      <c r="D29" s="37"/>
-      <c r="E29" s="37"/>
-      <c r="F29" s="37"/>
-      <c r="G29" s="38"/>
-      <c r="O29" s="3"/>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="2:22" ht="15" customHeight="1">
+      <c r="B29" s="13"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="15"/>
       <c r="P29" s="3"/>
       <c r="Q29" s="3"/>
       <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="2:21" ht="15.75" customHeight="1">
-      <c r="B30" s="36"/>
-      <c r="C30" s="37"/>
-      <c r="D30" s="37"/>
-      <c r="E30" s="37"/>
-      <c r="F30" s="37"/>
-      <c r="G30" s="38"/>
-      <c r="O30" s="3"/>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="2:22" ht="15.75" customHeight="1">
+      <c r="B30" s="13"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="15"/>
       <c r="P30" s="3"/>
       <c r="Q30" s="3"/>
       <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="2:21" ht="15.75" customHeight="1">
-      <c r="B31" s="36"/>
-      <c r="C31" s="37"/>
-      <c r="D31" s="37"/>
-      <c r="E31" s="37"/>
-      <c r="F31" s="37"/>
-      <c r="G31" s="38"/>
-      <c r="O31" s="3"/>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="2:22" ht="15.75" customHeight="1">
+      <c r="B31" s="13"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="15"/>
       <c r="P31" s="3"/>
       <c r="Q31" s="3"/>
       <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="2:21" ht="15.75" customHeight="1">
-      <c r="B32" s="36"/>
-      <c r="C32" s="37"/>
-      <c r="D32" s="37"/>
-      <c r="E32" s="37"/>
-      <c r="F32" s="37"/>
-      <c r="G32" s="38"/>
-      <c r="O32" s="3"/>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="2:22" ht="15.75" customHeight="1">
+      <c r="B32" s="13"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="15"/>
       <c r="P32" s="3"/>
       <c r="Q32" s="3"/>
       <c r="R32" s="3"/>
+      <c r="S32" s="3"/>
     </row>
     <row r="33" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B33" s="36"/>
-      <c r="C33" s="37"/>
-      <c r="D33" s="37"/>
-      <c r="E33" s="37"/>
-      <c r="F33" s="37"/>
-      <c r="G33" s="38"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="15"/>
     </row>
     <row r="34" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B34" s="39"/>
-      <c r="C34" s="40"/>
-      <c r="D34" s="40"/>
-      <c r="E34" s="40"/>
-      <c r="F34" s="40"/>
-      <c r="G34" s="41"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="18"/>
     </row>
     <row r="35" spans="2:7" ht="15.75" customHeight="1"/>
     <row r="36" spans="2:7" ht="15.75" customHeight="1"/>
@@ -2239,7 +2327,21 @@
     <row r="1000" ht="15.75" customHeight="1"/>
     <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="25">
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="S3:S4"/>
+    <mergeCell ref="P2:S2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="R3:R4"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="M3:N4"/>
     <mergeCell ref="B23:G34"/>
     <mergeCell ref="B19:G19"/>
     <mergeCell ref="B8:F8"/>
@@ -2251,19 +2353,6 @@
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B12:F12"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="B2:K2"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="R3:R4"/>
-    <mergeCell ref="O2:R2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="J3:K4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="H9:M9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>

--- a/sealand/CheckListSealand.xlsx
+++ b/sealand/CheckListSealand.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karinabanda/Desktop/Proyectos/Reportes/Reportes Diarios/Sealend/proyecto/sealand/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karinabanda/Desktop/Proyectos/Reportes/Reportes Diarios/proyecto/sealand/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13CCD5E9-C00A-274F-B9DC-0562FE64B4D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{490E1DD6-7CE2-9F4E-A142-1FB652E62F03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -78,13 +78,13 @@
     <t>Status</t>
   </si>
   <si>
-    <t>LOGS EN "darrow-database-web"</t>
-  </si>
-  <si>
     <t>La revisión realizada se basa en los siguientes criterios:
 * CPU Utilization: Confirmación de que el uso de CPU se mantenga por debajo del 85%.
 * Snapshot: Validación de la creación del respaldo correspondiente al día anterior en la RDS.
 Recomendación: No depender únicamente de los comentarios anexados; se sugiere realizar una revisión adicional para mayor precisión.</t>
+  </si>
+  <si>
+    <t>LOGS EN "ventura-entertainment"</t>
   </si>
 </sst>
 </file>
@@ -550,135 +550,135 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -922,70 +922,70 @@
   <sheetData>
     <row r="1" spans="2:22" ht="15.75" customHeight="1"/>
     <row r="2" spans="2:22" ht="27" customHeight="1">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="49"/>
-      <c r="P2" s="38" t="s">
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="30"/>
+      <c r="P2" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="39"/>
-      <c r="R2" s="39"/>
-      <c r="S2" s="39"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
+      <c r="S2" s="22"/>
     </row>
     <row r="3" spans="2:22" ht="27" customHeight="1">
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="41" t="s">
+      <c r="D3" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="41"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="40" t="s">
+      <c r="E3" s="26"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="41"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="40" t="s">
+      <c r="H3" s="26"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="K3" s="41"/>
-      <c r="L3" s="42"/>
-      <c r="M3" s="45" t="s">
+      <c r="K3" s="26"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="N3" s="43"/>
-      <c r="P3" s="36" t="s">
+      <c r="N3" s="32"/>
+      <c r="P3" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="Q3" s="36" t="s">
+      <c r="Q3" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="R3" s="36" t="s">
+      <c r="R3" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="S3" s="36" t="s">
+      <c r="S3" s="19" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="2:22" ht="22" customHeight="1">
-      <c r="B4" s="51"/>
-      <c r="C4" s="21"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="46"/>
       <c r="D4" s="9" t="s">
         <v>1</v>
       </c>
@@ -1013,25 +1013,25 @@
       <c r="L4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M4" s="46"/>
-      <c r="N4" s="44"/>
-      <c r="P4" s="37"/>
-      <c r="Q4" s="37"/>
-      <c r="R4" s="37"/>
-      <c r="S4" s="37"/>
+      <c r="M4" s="33"/>
+      <c r="N4" s="34"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="20"/>
+      <c r="S4" s="20"/>
     </row>
     <row r="5" spans="2:22" ht="15.75" customHeight="1">
-      <c r="B5" s="52"/>
+      <c r="B5" s="10"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="54"/>
-      <c r="L5" s="54"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
       <c r="M5" s="7"/>
       <c r="N5" s="6"/>
       <c r="P5" s="1"/>
@@ -1055,71 +1055,71 @@
       <c r="V7" s="4"/>
     </row>
     <row r="8" spans="2:22" ht="22" customHeight="1">
-      <c r="B8" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="20"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="H8" s="33" t="s">
+      <c r="B8" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="H8" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="I8" s="34"/>
-      <c r="J8" s="34"/>
-      <c r="K8" s="34"/>
-      <c r="L8" s="34"/>
-      <c r="M8" s="35"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="15"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
     </row>
     <row r="9" spans="2:22" ht="15.75" customHeight="1">
-      <c r="B9" s="30"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="31"/>
-      <c r="K9" s="31"/>
-      <c r="L9" s="31"/>
-      <c r="M9" s="32"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="18"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="18"/>
       <c r="P9" s="8"/>
       <c r="Q9" s="8"/>
       <c r="R9" s="8"/>
       <c r="S9" s="8"/>
     </row>
     <row r="10" spans="2:22" ht="15.75" customHeight="1">
-      <c r="B10" s="30"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="18"/>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
     </row>
     <row r="11" spans="2:22" ht="14" customHeight="1">
-      <c r="B11" s="30"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="18"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
     </row>
     <row r="12" spans="2:22" ht="13" customHeight="1">
-      <c r="B12" s="30"/>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="32"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="18"/>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
@@ -1144,14 +1144,14 @@
       <c r="S15" s="3"/>
     </row>
     <row r="16" spans="2:22" ht="23" customHeight="1">
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
-      <c r="G16" s="29"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="54"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
@@ -1159,12 +1159,12 @@
       <c r="V16" s="5"/>
     </row>
     <row r="17" spans="2:22" ht="15.75" customHeight="1">
-      <c r="B17" s="25"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="27"/>
+      <c r="B17" s="50"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="51"/>
+      <c r="G17" s="52"/>
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
@@ -1172,24 +1172,24 @@
       <c r="V17" s="5"/>
     </row>
     <row r="18" spans="2:22" ht="15.75" customHeight="1">
-      <c r="B18" s="25"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="27"/>
+      <c r="B18" s="50"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="51"/>
+      <c r="F18" s="51"/>
+      <c r="G18" s="52"/>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
       <c r="S18" s="3"/>
     </row>
     <row r="19" spans="2:22" ht="17" customHeight="1">
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
+      <c r="B19" s="44"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="44"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
@@ -1208,156 +1208,156 @@
       <c r="S21" s="3"/>
     </row>
     <row r="22" spans="2:22" ht="24" customHeight="1">
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="24"/>
+      <c r="C22" s="48"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="49"/>
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
       <c r="S22" s="3"/>
     </row>
     <row r="23" spans="2:22" ht="15" customHeight="1">
-      <c r="B23" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="12"/>
+      <c r="B23" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="37"/>
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
       <c r="S23" s="3"/>
     </row>
     <row r="24" spans="2:22" ht="15" customHeight="1">
-      <c r="B24" s="13"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="15"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="40"/>
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
       <c r="R24" s="3"/>
       <c r="S24" s="3"/>
     </row>
     <row r="25" spans="2:22" ht="17" customHeight="1">
-      <c r="B25" s="13"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="15"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="40"/>
       <c r="P25" s="3"/>
       <c r="Q25" s="3"/>
       <c r="R25" s="3"/>
       <c r="S25" s="3"/>
     </row>
     <row r="26" spans="2:22" ht="15" customHeight="1">
-      <c r="B26" s="13"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="15"/>
+      <c r="B26" s="38"/>
+      <c r="C26" s="39"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="40"/>
       <c r="P26" s="3"/>
       <c r="Q26" s="3"/>
       <c r="R26" s="3"/>
       <c r="S26" s="3"/>
     </row>
     <row r="27" spans="2:22" ht="15.75" customHeight="1">
-      <c r="B27" s="13"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="15"/>
+      <c r="B27" s="38"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="40"/>
       <c r="P27" s="3"/>
       <c r="Q27" s="3"/>
       <c r="R27" s="3"/>
       <c r="S27" s="3"/>
     </row>
     <row r="28" spans="2:22" ht="15.75" customHeight="1">
-      <c r="B28" s="13"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="15"/>
+      <c r="B28" s="38"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="40"/>
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
       <c r="R28" s="3"/>
       <c r="S28" s="3"/>
     </row>
     <row r="29" spans="2:22" ht="15" customHeight="1">
-      <c r="B29" s="13"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="15"/>
+      <c r="B29" s="38"/>
+      <c r="C29" s="39"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="39"/>
+      <c r="G29" s="40"/>
       <c r="P29" s="3"/>
       <c r="Q29" s="3"/>
       <c r="R29" s="3"/>
       <c r="S29" s="3"/>
     </row>
     <row r="30" spans="2:22" ht="15.75" customHeight="1">
-      <c r="B30" s="13"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="15"/>
+      <c r="B30" s="38"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="39"/>
+      <c r="G30" s="40"/>
       <c r="P30" s="3"/>
       <c r="Q30" s="3"/>
       <c r="R30" s="3"/>
       <c r="S30" s="3"/>
     </row>
     <row r="31" spans="2:22" ht="15.75" customHeight="1">
-      <c r="B31" s="13"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="15"/>
+      <c r="B31" s="38"/>
+      <c r="C31" s="39"/>
+      <c r="D31" s="39"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="39"/>
+      <c r="G31" s="40"/>
       <c r="P31" s="3"/>
       <c r="Q31" s="3"/>
       <c r="R31" s="3"/>
       <c r="S31" s="3"/>
     </row>
     <row r="32" spans="2:22" ht="15.75" customHeight="1">
-      <c r="B32" s="13"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="15"/>
+      <c r="B32" s="38"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="39"/>
+      <c r="F32" s="39"/>
+      <c r="G32" s="40"/>
       <c r="P32" s="3"/>
       <c r="Q32" s="3"/>
       <c r="R32" s="3"/>
       <c r="S32" s="3"/>
     </row>
     <row r="33" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B33" s="13"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="15"/>
+      <c r="B33" s="38"/>
+      <c r="C33" s="39"/>
+      <c r="D33" s="39"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="39"/>
+      <c r="G33" s="40"/>
     </row>
     <row r="34" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B34" s="16"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="18"/>
+      <c r="B34" s="41"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="43"/>
     </row>
     <row r="35" spans="2:7" ht="15.75" customHeight="1"/>
     <row r="36" spans="2:7" ht="15.75" customHeight="1"/>
@@ -2328,6 +2328,17 @@
     <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="B23:G34"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
     <mergeCell ref="H8:M8"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="S3:S4"/>
@@ -2342,17 +2353,6 @@
     <mergeCell ref="J3:L3"/>
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="M3:N4"/>
-    <mergeCell ref="B23:G34"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="B17:G17"/>
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>

--- a/sealand/CheckListSealand.xlsx
+++ b/sealand/CheckListSealand.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/karinabanda/Desktop/Proyectos/Reportes/Reportes Diarios/proyecto/sealand/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{490E1DD6-7CE2-9F4E-A142-1FB652E62F03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E26ACAB4-01D7-DA45-8EF1-FF3A14ADFF91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
   <si>
     <t>CPU Utilization Last Hour</t>
   </si>
@@ -535,7 +535,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -553,6 +553,75 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -562,15 +631,6 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -604,9 +664,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -618,66 +675,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -922,70 +919,62 @@
   <sheetData>
     <row r="1" spans="2:22" ht="15.75" customHeight="1"/>
     <row r="2" spans="2:22" ht="27" customHeight="1">
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="30"/>
-      <c r="P2" s="21" t="s">
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
+      <c r="P2" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
-      <c r="S2" s="22"/>
+      <c r="Q2" s="42"/>
+      <c r="R2" s="42"/>
+      <c r="S2" s="42"/>
     </row>
     <row r="3" spans="2:22" ht="27" customHeight="1">
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="46" t="s">
+      <c r="C3" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="D3" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="26"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="25" t="s">
+      <c r="E3" s="46"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="26"/>
-      <c r="I3" s="27"/>
-      <c r="J3" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="K3" s="26"/>
-      <c r="L3" s="27"/>
-      <c r="M3" s="31" t="s">
+      <c r="H3" s="46"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="N3" s="32"/>
-      <c r="P3" s="19" t="s">
+      <c r="K3" s="51"/>
+      <c r="P3" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="Q3" s="19" t="s">
+      <c r="Q3" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="R3" s="19" t="s">
+      <c r="R3" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="S3" s="19" t="s">
+      <c r="S3" s="39" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="2:22" ht="22" customHeight="1">
-      <c r="B4" s="24"/>
-      <c r="C4" s="46"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="24"/>
       <c r="D4" s="9" t="s">
         <v>1</v>
       </c>
@@ -1004,21 +993,12 @@
       <c r="I4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4" s="33"/>
-      <c r="N4" s="34"/>
-      <c r="P4" s="20"/>
-      <c r="Q4" s="20"/>
-      <c r="R4" s="20"/>
-      <c r="S4" s="20"/>
+      <c r="J4" s="52"/>
+      <c r="K4" s="53"/>
+      <c r="P4" s="40"/>
+      <c r="Q4" s="40"/>
+      <c r="R4" s="40"/>
+      <c r="S4" s="40"/>
     </row>
     <row r="5" spans="2:22" ht="15.75" customHeight="1">
       <c r="B5" s="10"/>
@@ -1029,11 +1009,8 @@
       <c r="G5" s="12"/>
       <c r="H5" s="12"/>
       <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="6"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="6"/>
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
@@ -1055,71 +1032,71 @@
       <c r="V7" s="4"/>
     </row>
     <row r="8" spans="2:22" ht="22" customHeight="1">
-      <c r="B8" s="45" t="s">
+      <c r="B8" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
-      <c r="H8" s="13" t="s">
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
+      <c r="H8" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14"/>
-      <c r="M8" s="15"/>
+      <c r="I8" s="37"/>
+      <c r="J8" s="37"/>
+      <c r="K8" s="37"/>
+      <c r="L8" s="37"/>
+      <c r="M8" s="38"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
     </row>
     <row r="9" spans="2:22" ht="15.75" customHeight="1">
-      <c r="B9" s="16"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="18"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="18"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="35"/>
+      <c r="H9" s="33"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="34"/>
+      <c r="K9" s="34"/>
+      <c r="L9" s="34"/>
+      <c r="M9" s="35"/>
       <c r="P9" s="8"/>
       <c r="Q9" s="8"/>
       <c r="R9" s="8"/>
       <c r="S9" s="8"/>
     </row>
     <row r="10" spans="2:22" ht="15.75" customHeight="1">
-      <c r="B10" s="16"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="18"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="35"/>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
     </row>
     <row r="11" spans="2:22" ht="14" customHeight="1">
-      <c r="B11" s="16"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="18"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="35"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
     </row>
     <row r="12" spans="2:22" ht="13" customHeight="1">
-      <c r="B12" s="16"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="18"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="35"/>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
@@ -1144,14 +1121,14 @@
       <c r="S15" s="3"/>
     </row>
     <row r="16" spans="2:22" ht="23" customHeight="1">
-      <c r="B16" s="53" t="s">
+      <c r="B16" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="54"/>
-      <c r="D16" s="54"/>
-      <c r="E16" s="54"/>
-      <c r="F16" s="54"/>
-      <c r="G16" s="54"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
@@ -1159,12 +1136,12 @@
       <c r="V16" s="5"/>
     </row>
     <row r="17" spans="2:22" ht="15.75" customHeight="1">
-      <c r="B17" s="50"/>
-      <c r="C17" s="51"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="51"/>
-      <c r="F17" s="51"/>
-      <c r="G17" s="52"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="30"/>
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
@@ -1172,24 +1149,24 @@
       <c r="V17" s="5"/>
     </row>
     <row r="18" spans="2:22" ht="15.75" customHeight="1">
-      <c r="B18" s="50"/>
-      <c r="C18" s="51"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="51"/>
-      <c r="F18" s="51"/>
-      <c r="G18" s="52"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="30"/>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
       <c r="S18" s="3"/>
     </row>
     <row r="19" spans="2:22" ht="17" customHeight="1">
-      <c r="B19" s="44"/>
-      <c r="C19" s="44"/>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
@@ -1208,156 +1185,156 @@
       <c r="S21" s="3"/>
     </row>
     <row r="22" spans="2:22" ht="24" customHeight="1">
-      <c r="B22" s="47" t="s">
+      <c r="B22" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="48"/>
-      <c r="D22" s="48"/>
-      <c r="E22" s="48"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="49"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="27"/>
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
       <c r="S22" s="3"/>
     </row>
     <row r="23" spans="2:22" ht="15" customHeight="1">
-      <c r="B23" s="35" t="s">
+      <c r="B23" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-      <c r="G23" s="37"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="15"/>
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
       <c r="S23" s="3"/>
     </row>
     <row r="24" spans="2:22" ht="15" customHeight="1">
-      <c r="B24" s="38"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="40"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="18"/>
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
       <c r="R24" s="3"/>
       <c r="S24" s="3"/>
     </row>
     <row r="25" spans="2:22" ht="17" customHeight="1">
-      <c r="B25" s="38"/>
-      <c r="C25" s="39"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="40"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="18"/>
       <c r="P25" s="3"/>
       <c r="Q25" s="3"/>
       <c r="R25" s="3"/>
       <c r="S25" s="3"/>
     </row>
     <row r="26" spans="2:22" ht="15" customHeight="1">
-      <c r="B26" s="38"/>
-      <c r="C26" s="39"/>
-      <c r="D26" s="39"/>
-      <c r="E26" s="39"/>
-      <c r="F26" s="39"/>
-      <c r="G26" s="40"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="18"/>
       <c r="P26" s="3"/>
       <c r="Q26" s="3"/>
       <c r="R26" s="3"/>
       <c r="S26" s="3"/>
     </row>
     <row r="27" spans="2:22" ht="15.75" customHeight="1">
-      <c r="B27" s="38"/>
-      <c r="C27" s="39"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="39"/>
-      <c r="F27" s="39"/>
-      <c r="G27" s="40"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="18"/>
       <c r="P27" s="3"/>
       <c r="Q27" s="3"/>
       <c r="R27" s="3"/>
       <c r="S27" s="3"/>
     </row>
     <row r="28" spans="2:22" ht="15.75" customHeight="1">
-      <c r="B28" s="38"/>
-      <c r="C28" s="39"/>
-      <c r="D28" s="39"/>
-      <c r="E28" s="39"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="40"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="18"/>
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
       <c r="R28" s="3"/>
       <c r="S28" s="3"/>
     </row>
     <row r="29" spans="2:22" ht="15" customHeight="1">
-      <c r="B29" s="38"/>
-      <c r="C29" s="39"/>
-      <c r="D29" s="39"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="39"/>
-      <c r="G29" s="40"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="18"/>
       <c r="P29" s="3"/>
       <c r="Q29" s="3"/>
       <c r="R29" s="3"/>
       <c r="S29" s="3"/>
     </row>
     <row r="30" spans="2:22" ht="15.75" customHeight="1">
-      <c r="B30" s="38"/>
-      <c r="C30" s="39"/>
-      <c r="D30" s="39"/>
-      <c r="E30" s="39"/>
-      <c r="F30" s="39"/>
-      <c r="G30" s="40"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="18"/>
       <c r="P30" s="3"/>
       <c r="Q30" s="3"/>
       <c r="R30" s="3"/>
       <c r="S30" s="3"/>
     </row>
     <row r="31" spans="2:22" ht="15.75" customHeight="1">
-      <c r="B31" s="38"/>
-      <c r="C31" s="39"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="39"/>
-      <c r="F31" s="39"/>
-      <c r="G31" s="40"/>
+      <c r="B31" s="16"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="18"/>
       <c r="P31" s="3"/>
       <c r="Q31" s="3"/>
       <c r="R31" s="3"/>
       <c r="S31" s="3"/>
     </row>
     <row r="32" spans="2:22" ht="15.75" customHeight="1">
-      <c r="B32" s="38"/>
-      <c r="C32" s="39"/>
-      <c r="D32" s="39"/>
-      <c r="E32" s="39"/>
-      <c r="F32" s="39"/>
-      <c r="G32" s="40"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="18"/>
       <c r="P32" s="3"/>
       <c r="Q32" s="3"/>
       <c r="R32" s="3"/>
       <c r="S32" s="3"/>
     </row>
     <row r="33" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B33" s="38"/>
-      <c r="C33" s="39"/>
-      <c r="D33" s="39"/>
-      <c r="E33" s="39"/>
-      <c r="F33" s="39"/>
-      <c r="G33" s="40"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="18"/>
     </row>
     <row r="34" spans="2:7" ht="15.75" customHeight="1">
-      <c r="B34" s="41"/>
-      <c r="C34" s="42"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="43"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="21"/>
     </row>
     <row r="35" spans="2:7" ht="15.75" customHeight="1"/>
     <row r="36" spans="2:7" ht="15.75" customHeight="1"/>
@@ -2327,7 +2304,20 @@
     <row r="1000" ht="15.75" customHeight="1"/>
     <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="24">
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="S3:S4"/>
+    <mergeCell ref="P2:S2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="R3:R4"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="J3:K4"/>
+    <mergeCell ref="B2:K2"/>
     <mergeCell ref="B23:G34"/>
     <mergeCell ref="B19:G19"/>
     <mergeCell ref="B8:F8"/>
@@ -2339,20 +2329,6 @@
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B12:F12"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="S3:S4"/>
-    <mergeCell ref="P2:S2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="R3:R4"/>
-    <mergeCell ref="H9:M9"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="B2:N2"/>
-    <mergeCell ref="M3:N4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
